--- a/WeeklyPredictions.xlsx
+++ b/WeeklyPredictions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkArea\Workspaces\ProfessionalCourses\AI-ML_CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4A9FF8-3F18-4ADB-81AC-CB1884AAD7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D06F9D-E08C-4026-AAF3-1646E3E5CAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="354" yWindow="600" windowWidth="22500" windowHeight="12852" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="354" yWindow="600" windowWidth="22500" windowHeight="12852" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Function 1" sheetId="1" r:id="rId1"/>

--- a/WeeklyPredictions.xlsx
+++ b/WeeklyPredictions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkArea\Workspaces\ProfessionalCourses\AI-ML_CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D06F9D-E08C-4026-AAF3-1646E3E5CAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369F7F80-D2F0-4658-A85A-78463E02E457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="354" yWindow="600" windowWidth="22500" windowHeight="12852" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="58440" yWindow="600" windowWidth="36765" windowHeight="19575" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Function 1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Function 8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="91">
   <si>
     <t>Input (feature) dimension:</t>
   </si>
@@ -360,6 +361,127 @@
   <si>
     <t>[0.998499, 0.999000, 0.999500, 1.000000]</t>
   </si>
+  <si>
+    <t>[0.184184, 0.185185]</t>
+  </si>
+  <si>
+    <t>[0.288288, 0.289289]</t>
+  </si>
+  <si>
+    <t>[0.524524, 0.525525]</t>
+  </si>
+  <si>
+    <t>Heuristic based on function graph</t>
+  </si>
+  <si>
+    <t>[1.000000, 1.000000, 1.000000, 1.000000]</t>
+  </si>
+  <si>
+    <t>[0.418167, 0.418567, 0.418968, 0.419368, 0.419768]</t>
+  </si>
+  <si>
+    <t>Matern(length_scale=1.0, length_scale_bounds=(1e-3, 1e3), nu=np.inf)</t>
+  </si>
+  <si>
+    <t>[0.414166, 0.414566, 0.414966, 0.415366, 0.415766]</t>
+  </si>
+  <si>
+    <t>Heuristic based on function graph and permutation importance</t>
+  </si>
+  <si>
+    <t>[0.060000, 0.400000, 0.200000, 0.250000, 0.400000, 0.700000]</t>
+  </si>
+  <si>
+    <t>[0.226057, 0.226307, 0.226557, 0.226807, 0.227057, 0.227307, 0.227557, 0.227807]</t>
+  </si>
+  <si>
+    <t>[0.204051, 0.204301, 0.204551, 0.204801, 0.205051, 0.205301, 0.205551, 0.205801]</t>
+  </si>
+  <si>
+    <t>[0.898898, 0.899899]</t>
+  </si>
+  <si>
+    <t>RBF(length_scale=10.0, length_scale_bounds=(1e-3, 1e3))</t>
+  </si>
+  <si>
+    <t>[0.856856, 0.857857]</t>
+  </si>
+  <si>
+    <t>[0.000000, 0.000000]</t>
+  </si>
+  <si>
+    <r>
+      <t>RBF(length_scale=10.0, length_scale_bounds=(1e-3, 1e3)), GPR.alpha=1e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-05</t>
+    </r>
+  </si>
+  <si>
+    <t>[0.748499, 0.749166, 0.749833]</t>
+  </si>
+  <si>
+    <t>RBF(length_scale=1.0, length_scale_bounds=(1e-3, 1e3))</t>
+  </si>
+  <si>
+    <t>[0.348174, 0.348674, 0.349174, 0.349674]</t>
+  </si>
+  <si>
+    <t>[0.920000, 0.920000, 0.920000, 0.920000]</t>
+  </si>
+  <si>
+    <t>Matern(length_scale=0.1, length_scale_bounds=(1e-3, 1e3), nu=np.inf)</t>
+  </si>
+  <si>
+    <t>[0.998399, 0.998799, 0.999199, 0.999599, 1.000000]</t>
+  </si>
+  <si>
+    <t>[0.254084, 0.254418, 0.254751, 0.255085, 0.255418, 0.255751]</t>
+  </si>
+  <si>
+    <t>RationalQuadratic(length_scale=0.1, length_scale_bounds=(1e-3, 1e3))</t>
+  </si>
+  <si>
+    <t>[0.212053, 0.212303, 0.212553, 0.212803, 0.213053, 0.213303, 0.213553, 0.213803]</t>
+  </si>
+  <si>
+    <t>Matern(length_scale=0.01, length_scale_bounds=(1e-2, 1e2), nu=1.5)</t>
+  </si>
+  <si>
+    <t>[0.384384, 0.385385]</t>
+  </si>
+  <si>
+    <t>[0.750000, 0.900000]</t>
+  </si>
+  <si>
+    <t>Matern(length_scale=0.01, length_scale_bounds=(1e-3, 1e3), nu=1.5)</t>
+  </si>
+  <si>
+    <t>[0.542000, 0.550000, 0.566000]</t>
+  </si>
+  <si>
+    <t>[0.358179, 0.358679, 0.359179, 0.359679]</t>
+  </si>
+  <si>
+    <t>[0.998499, 0.998999, 0.999499, 1.000000]</t>
+  </si>
+  <si>
+    <t>[0.452180, 0.452581, 0.452981, 0.700000, 0.060000]</t>
+  </si>
+  <si>
+    <t>[0.334111, 0.334444, 0.334778, 0.335111, 0.335445, 0.680000]</t>
+  </si>
+  <si>
+    <t>[0.070000, 0.046261, 0.100000, 0.100000, 0.047011, 0.047261, 0.047511, 0.047761]</t>
+  </si>
 </sst>
 </file>
 
@@ -622,7 +744,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -719,8 +841,22 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -728,11 +864,8 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1046,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:N28"/>
+  <dimension ref="B3:N31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.3125" customWidth="1"/>
@@ -1064,36 +1197,36 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="38.4" customHeight="1">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="G7" s="38" t="s">
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="G7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
       <c r="K7" s="1"/>
       <c r="L7" s="14" t="s">
         <v>6</v>
@@ -1130,174 +1263,174 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="38"/>
       <c r="D9">
         <v>0.31940389000000002</v>
       </c>
       <c r="E9">
         <v>0.76295937000000003</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
       <c r="J9" s="4">
         <v>1.3226770399999999E-79</v>
       </c>
       <c r="K9" s="4"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10">
         <v>0.57432921000000003</v>
       </c>
       <c r="E10">
         <v>0.87989810000000002</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
       <c r="J10" s="4">
         <v>1.0330782399999999E-46</v>
       </c>
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
       <c r="D11">
         <v>0.73102363000000004</v>
       </c>
       <c r="E11">
         <v>0.73299988000000005</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
       <c r="J11" s="4">
         <v>7.7108751100000005E-16</v>
       </c>
       <c r="K11" s="4"/>
     </row>
     <row r="12" spans="2:14">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12">
         <v>0.84035342000000002</v>
       </c>
       <c r="E12">
         <v>0.26473161000000001</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
       <c r="J12" s="6">
         <v>3.3417710099999998E-124</v>
       </c>
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13">
         <v>0.65011406000000005</v>
       </c>
       <c r="E13">
         <v>0.68152634999999995</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
       <c r="J13" s="4">
         <v>-3.6060626400000002E-3</v>
       </c>
       <c r="K13" s="4"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
       <c r="D14">
         <v>0.41043713999999998</v>
       </c>
       <c r="E14">
         <v>0.1475543</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
       <c r="J14" s="4">
         <v>-2.15924904E-54</v>
       </c>
       <c r="K14" s="4"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
       <c r="D15">
         <v>0.31269116000000002</v>
       </c>
       <c r="E15">
         <v>7.8722780000000006E-2</v>
       </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
       <c r="J15" s="6">
         <v>-2.0890932699999999E-91</v>
       </c>
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="2:14">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16">
         <v>0.68341817000000005</v>
       </c>
       <c r="E16">
         <v>0.86105746000000005</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
       <c r="J16" s="6">
         <v>2.5350011499999998E-40</v>
       </c>
       <c r="K16" s="6"/>
     </row>
     <row r="17" spans="2:14">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17">
         <v>8.2507250000000004E-2</v>
       </c>
       <c r="E17">
         <v>0.40348750999999999</v>
       </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
       <c r="J17" s="6">
         <v>3.6067711900000002E-81</v>
       </c>
       <c r="K17" s="6"/>
     </row>
     <row r="18" spans="2:14">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18">
         <v>0.88388982999999999</v>
       </c>
       <c r="E18">
         <v>0.58225397000000001</v>
       </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
       <c r="J18" s="6">
         <v>6.2298564700000004E-48</v>
       </c>
@@ -1437,14 +1570,171 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="2:14">
-      <c r="N26" s="5"/>
-    </row>
-    <row r="27" spans="2:14">
+    <row r="25" spans="2:14">
+      <c r="B25" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="23">
+        <v>3</v>
+      </c>
+      <c r="D25" s="27">
+        <v>0.99899899999999997</v>
+      </c>
+      <c r="E25" s="27">
+        <v>1</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="24">
+        <v>3</v>
+      </c>
+      <c r="I25" s="24"/>
+      <c r="J25" s="28">
+        <v>4.7383981465482201E-192</v>
+      </c>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+    </row>
+    <row r="26" spans="2:14" ht="28.8">
+      <c r="G26" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="13">
+        <f>MAX(L23,J25)</f>
+        <v>2.6752879910742401E-9</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" ht="28.8">
+      <c r="G27" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="13">
+        <f>MAX(L23,J25)</f>
+        <v>2.6752879910742401E-9</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="N27" s="2"/>
     </row>
     <row r="28" spans="2:14">
-      <c r="N28" s="2"/>
+      <c r="B28" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="23">
+        <v>4</v>
+      </c>
+      <c r="D28" s="27">
+        <v>0.18418399999999999</v>
+      </c>
+      <c r="E28" s="27">
+        <v>0.18518499999999999</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="24">
+        <v>4</v>
+      </c>
+      <c r="I28" s="24"/>
+      <c r="J28" s="28">
+        <v>1.21844591337822E-78</v>
+      </c>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24"/>
+    </row>
+    <row r="29" spans="2:14" ht="43.2">
+      <c r="G29" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L29" s="13">
+        <f>MAX(L26,J28)</f>
+        <v>2.6752879910742401E-9</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N29" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="23">
+        <v>5</v>
+      </c>
+      <c r="D30" s="27">
+        <v>0.89889799999999997</v>
+      </c>
+      <c r="E30" s="27">
+        <v>0.899899</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="24">
+        <v>5</v>
+      </c>
+      <c r="I30" s="24"/>
+      <c r="J30" s="28">
+        <v>5.5889990975819399E-104</v>
+      </c>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="24"/>
+    </row>
+    <row r="31" spans="2:14" ht="43.2">
+      <c r="G31" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L31" s="13">
+        <f>MAX(L29,J30)</f>
+        <v>2.6752879910742401E-9</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N31" s="29" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1462,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{670CB941-049A-4FC0-8F09-1656ED8CE3C7}">
-  <dimension ref="B3:N29"/>
+  <dimension ref="B3:N32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -1480,36 +1770,36 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="38.4" customHeight="1">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="G7" s="38" t="s">
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="G7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
       <c r="K7" s="1"/>
       <c r="L7" s="14" t="s">
         <v>6</v>
@@ -1546,174 +1836,174 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="38"/>
       <c r="D9">
         <v>0.66579957999999995</v>
       </c>
       <c r="E9" s="22">
         <v>0.12396913</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
       <c r="J9" s="20">
         <v>0.53899611999999997</v>
       </c>
       <c r="K9" s="4"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="22">
         <v>0.87779099000000005</v>
       </c>
       <c r="E10" s="22">
         <v>0.77862750000000003</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
       <c r="J10" s="20">
         <v>0.42058624</v>
       </c>
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="22">
         <v>0.14269907000000001</v>
       </c>
       <c r="E11" s="22">
         <v>0.34900513</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
       <c r="J11" s="20">
         <v>-6.5623619999999994E-2</v>
       </c>
       <c r="K11" s="4"/>
     </row>
     <row r="12" spans="2:14">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="22">
         <v>0.84527543000000005</v>
       </c>
       <c r="E12" s="22">
         <v>0.71112027</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
       <c r="J12" s="20">
         <v>0.29399291</v>
       </c>
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="22">
         <v>0.45464714000000001</v>
       </c>
       <c r="E13" s="22">
         <v>0.29045517999999998</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
       <c r="J13" s="20">
         <v>0.21496451</v>
       </c>
       <c r="K13" s="20"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="22">
         <v>0.57771284000000001</v>
       </c>
       <c r="E14" s="22">
         <v>0.77197318000000004</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
       <c r="J14" s="20">
         <v>2.3105549999999999E-2</v>
       </c>
       <c r="K14" s="4"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="22">
         <v>0.43816606000000002</v>
       </c>
       <c r="E15" s="22">
         <v>0.68501825999999999</v>
       </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
       <c r="J15" s="20">
         <v>0.24461933999999999</v>
       </c>
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="2:14">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="22">
         <v>0.34174958999999999</v>
       </c>
       <c r="E16" s="22">
         <v>2.8697719999999999E-2</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
       <c r="J16" s="20">
         <v>3.8749020000000002E-2</v>
       </c>
       <c r="K16" s="6"/>
     </row>
     <row r="17" spans="2:14">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="22">
         <v>0.33864815999999998</v>
       </c>
       <c r="E17" s="22">
         <v>0.21386725000000001</v>
       </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
       <c r="J17" s="20">
         <v>-1.3857619999999999E-2</v>
       </c>
       <c r="K17" s="6"/>
     </row>
     <row r="18" spans="2:14">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="22">
         <v>0.70263655999999997</v>
       </c>
       <c r="E18" s="22">
         <v>0.92656419999999995</v>
       </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
       <c r="J18" s="20">
         <v>0.61120521999999999</v>
       </c>
@@ -1769,7 +2059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="32.700000000000003" customHeight="1">
+    <row r="21" spans="2:14" ht="68.7" customHeight="1">
       <c r="G21" s="19" t="s">
         <v>18</v>
       </c>
@@ -1806,9 +2096,7 @@
       <c r="H22" s="24">
         <v>2</v>
       </c>
-      <c r="I22" s="24" t="s">
-        <v>12</v>
-      </c>
+      <c r="I22" s="24"/>
       <c r="J22" s="26">
         <v>2.8722774311624101E-2</v>
       </c>
@@ -1835,7 +2123,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="45.3">
+    <row r="24" spans="2:14" ht="59.7" customHeight="1">
       <c r="G24" s="19" t="s">
         <v>40</v>
       </c>
@@ -1856,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="45.3">
+    <row r="25" spans="2:14" ht="63.3" customHeight="1">
       <c r="G25" s="19" t="s">
         <v>38</v>
       </c>
@@ -1875,18 +2163,158 @@
       </c>
     </row>
     <row r="26" spans="2:14">
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="L26" s="21"/>
-    </row>
-    <row r="27" spans="2:14">
-      <c r="N27" s="5"/>
-    </row>
-    <row r="28" spans="2:14">
-      <c r="N28" s="2"/>
+      <c r="B26" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="23">
+        <v>3</v>
+      </c>
+      <c r="D26" s="27">
+        <v>0.47447400000000001</v>
+      </c>
+      <c r="E26" s="27">
+        <v>0.47547499999999998</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="24">
+        <v>3</v>
+      </c>
+      <c r="I26" s="24"/>
+      <c r="J26" s="26">
+        <v>0.65954311857258696</v>
+      </c>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="24"/>
+    </row>
+    <row r="27" spans="2:14" ht="45.3">
+      <c r="G27" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="21">
+        <f>MAX(L24,J26)</f>
+        <v>0.70032323557308995</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="2:14" ht="36.9" customHeight="1">
+      <c r="G28" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="21">
+        <f>MAX(L24,J26)</f>
+        <v>0.70032323557308995</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N28" s="29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="2:14">
-      <c r="N29" s="2"/>
+      <c r="B29" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="23">
+        <v>4</v>
+      </c>
+      <c r="D29" s="27">
+        <v>0</v>
+      </c>
+      <c r="E29" s="27">
+        <v>0</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="24">
+        <v>4</v>
+      </c>
+      <c r="I29" s="24"/>
+      <c r="J29" s="26">
+        <v>-9.6034610514321606E-2</v>
+      </c>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+    </row>
+    <row r="30" spans="2:14" ht="46.2" customHeight="1">
+      <c r="G30" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="21">
+        <f>MAX(L28,J29)</f>
+        <v>0.70032323557308995</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N30" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="23">
+        <v>5</v>
+      </c>
+      <c r="D31" s="27">
+        <v>0.85685599999999995</v>
+      </c>
+      <c r="E31" s="27">
+        <v>0.85785699999999998</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="24">
+        <v>5</v>
+      </c>
+      <c r="I31" s="24"/>
+      <c r="J31" s="26">
+        <v>0.22080276057040199</v>
+      </c>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+    </row>
+    <row r="32" spans="2:14" ht="31.8" customHeight="1">
+      <c r="G32" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="21">
+        <f>MAX(L30,J31)</f>
+        <v>0.70032323557308995</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N32" s="29" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1904,7 +2332,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31898AF6-32B3-4A29-BBAB-B50A72E3787B}">
-  <dimension ref="B3:O30"/>
+  <dimension ref="B3:O36"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -1922,37 +2350,37 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:15">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="38.4" customHeight="1">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="7"/>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
       <c r="L7" s="1"/>
       <c r="M7" s="14" t="s">
         <v>6</v>
@@ -1965,8 +2393,8 @@
       </c>
     </row>
     <row r="8" spans="2:15" ht="21.3">
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="16" t="s">
         <v>13</v>
       </c>
@@ -1992,10 +2420,10 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="22">
         <v>0.17152521000000001</v>
       </c>
@@ -2005,19 +2433,19 @@
       <c r="F9" s="22">
         <v>0.24873719999999999</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
       <c r="K9" s="20">
         <v>-0.11212220000000001</v>
       </c>
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="2:15">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="22">
         <v>0.24211446</v>
       </c>
@@ -2027,17 +2455,17 @@
       <c r="F10" s="22">
         <v>0.27243281000000003</v>
       </c>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
       <c r="K10" s="20">
         <v>-8.7962860000000004E-2</v>
       </c>
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="2:15">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="22">
         <v>0.53490572000000003</v>
       </c>
@@ -2047,17 +2475,17 @@
       <c r="F11" s="22">
         <v>0.17338872999999999</v>
       </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
       <c r="K11" s="20">
         <v>-0.11141465</v>
       </c>
       <c r="L11" s="4"/>
     </row>
     <row r="12" spans="2:15">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="22">
         <v>0.49258141</v>
       </c>
@@ -2067,17 +2495,17 @@
       <c r="F12" s="22">
         <v>0.34017639</v>
       </c>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
       <c r="K12" s="20">
         <v>-3.4835310000000001E-2</v>
       </c>
       <c r="L12" s="6"/>
     </row>
     <row r="13" spans="2:15">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="22">
         <v>0.13462167</v>
       </c>
@@ -2087,17 +2515,17 @@
       <c r="F13" s="22">
         <v>0.45820622</v>
       </c>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
       <c r="K13" s="20">
         <v>-4.8007580000000001E-2</v>
       </c>
       <c r="L13" s="20"/>
     </row>
     <row r="14" spans="2:15">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="22">
         <v>0.34552326999999999</v>
       </c>
@@ -2107,17 +2535,17 @@
       <c r="F14" s="22">
         <v>0.26936347999999999</v>
       </c>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
       <c r="K14" s="20">
         <v>-0.11062091</v>
       </c>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="2:15">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="22">
         <v>0.15183663</v>
       </c>
@@ -2127,17 +2555,17 @@
       <c r="F15" s="22">
         <v>0.99088187000000005</v>
       </c>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
       <c r="K15" s="20">
         <v>-0.39892550999999998</v>
       </c>
       <c r="L15" s="6"/>
     </row>
     <row r="16" spans="2:15">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="22">
         <v>0.64550284000000002</v>
       </c>
@@ -2147,17 +2575,17 @@
       <c r="F16" s="22">
         <v>0.91977134000000005</v>
       </c>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
       <c r="K16" s="20">
         <v>-0.11386851000000001</v>
       </c>
       <c r="L16" s="6"/>
     </row>
     <row r="17" spans="2:15">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="22">
         <v>0.74691194999999999</v>
       </c>
@@ -2167,17 +2595,17 @@
       <c r="F17" s="22">
         <v>0.22629985</v>
       </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
       <c r="K17" s="20">
         <v>-0.13146061000000001</v>
       </c>
       <c r="L17" s="6"/>
     </row>
     <row r="18" spans="2:15">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="22">
         <v>0.17047698999999999</v>
       </c>
@@ -2187,17 +2615,17 @@
       <c r="F18" s="22">
         <v>0.14916942999999999</v>
       </c>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
       <c r="K18" s="20">
         <v>-9.4189560000000006E-2</v>
       </c>
       <c r="L18" s="6"/>
     </row>
     <row r="19" spans="2:15">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="22">
         <v>0.22054934000000001</v>
       </c>
@@ -2207,17 +2635,17 @@
       <c r="F19" s="22">
         <v>0.34355533999999999</v>
       </c>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
       <c r="K19" s="20">
         <v>-4.6947410000000002E-2</v>
       </c>
       <c r="L19" s="6"/>
     </row>
     <row r="20" spans="2:15">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="22">
         <v>0.66601365999999995</v>
       </c>
@@ -2227,17 +2655,17 @@
       <c r="F20" s="22">
         <v>0.24629529999999999</v>
       </c>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
       <c r="K20" s="20">
         <v>-0.10596504</v>
       </c>
       <c r="L20" s="6"/>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="22">
         <v>4.6808950000000002E-2</v>
       </c>
@@ -2247,17 +2675,17 @@
       <c r="F21" s="22">
         <v>0.77061758999999996</v>
       </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
       <c r="K21" s="20">
         <v>-0.11804826</v>
       </c>
       <c r="L21" s="6"/>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="22">
         <v>0.60009727999999996</v>
       </c>
@@ -2267,17 +2695,17 @@
       <c r="F22" s="22">
         <v>6.6088640000000004E-2</v>
       </c>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
       <c r="K22" s="20">
         <v>-3.637783E-2</v>
       </c>
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="22">
         <v>0.96599484999999996</v>
       </c>
@@ -2287,9 +2715,9 @@
       <c r="F23" s="22">
         <v>0.56682913000000001</v>
       </c>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
       <c r="K23" s="20">
         <v>-5.6758370000000002E-2</v>
       </c>
@@ -2388,9 +2816,7 @@
       <c r="I27" s="24">
         <v>2</v>
       </c>
-      <c r="J27" s="24" t="s">
-        <v>12</v>
-      </c>
+      <c r="J27" s="24"/>
       <c r="K27" s="26">
         <v>-0.47577599999999998</v>
       </c>
@@ -2440,7 +2866,172 @@
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="2:15">
-      <c r="O30" s="2"/>
+      <c r="B30" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="23">
+        <v>3</v>
+      </c>
+      <c r="D30" s="27">
+        <v>0.41827900000000001</v>
+      </c>
+      <c r="E30" s="27">
+        <v>0.41894599999999999</v>
+      </c>
+      <c r="F30" s="27">
+        <v>0.41961300000000001</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="24">
+        <v>3</v>
+      </c>
+      <c r="J30" s="24"/>
+      <c r="K30" s="26">
+        <v>-3.4320243437859901E-2</v>
+      </c>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="24"/>
+    </row>
+    <row r="31" spans="2:15" ht="37.200000000000003" customHeight="1">
+      <c r="H31" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M31" s="21">
+        <f>MAX(M28,K30)</f>
+        <v>-3.7555388348285302E-3</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O31" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" ht="43.2">
+      <c r="H32" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M32" s="21">
+        <f>MAX(M28,K30)</f>
+        <v>-3.7555388348285302E-3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15">
+      <c r="B33" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="23">
+        <v>4</v>
+      </c>
+      <c r="D33" s="27">
+        <v>0</v>
+      </c>
+      <c r="E33" s="27">
+        <v>6.6699999999999995E-4</v>
+      </c>
+      <c r="F33" s="27">
+        <v>1.3339999999999999E-3</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="24">
+        <v>4</v>
+      </c>
+      <c r="J33" s="24"/>
+      <c r="K33" s="26">
+        <v>-0.16923058367993099</v>
+      </c>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+    </row>
+    <row r="34" spans="2:15" ht="43.2">
+      <c r="H34" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M34" s="21">
+        <f>MAX(M31,K33)</f>
+        <v>-3.7555388348285302E-3</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O34" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15">
+      <c r="B35" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="23">
+        <v>5</v>
+      </c>
+      <c r="D35" s="27">
+        <v>0.74849900000000003</v>
+      </c>
+      <c r="E35" s="27">
+        <v>0.749166</v>
+      </c>
+      <c r="F35" s="27">
+        <v>0.74983299999999997</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="24">
+        <v>5</v>
+      </c>
+      <c r="J35" s="24"/>
+      <c r="K35" s="26">
+        <v>-0.123204361989619</v>
+      </c>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+    </row>
+    <row r="36" spans="2:15" ht="28.8">
+      <c r="H36" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M36" s="21">
+        <f>MAX(M34,K35)</f>
+        <v>-3.7555388348285302E-3</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O36" s="32" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2459,7 +3050,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7581826F-7241-48DF-A0E8-08483F533A08}">
-  <dimension ref="B3:P46"/>
+  <dimension ref="B3:P50"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -2477,38 +3068,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:16">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="38.4" customHeight="1">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
       <c r="M7" s="1"/>
       <c r="N7" s="14" t="s">
         <v>6</v>
@@ -2521,8 +3112,8 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="21.3">
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="16" t="s">
         <v>13</v>
       </c>
@@ -2551,10 +3142,10 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="22">
         <v>0.89698104999999995</v>
       </c>
@@ -2567,19 +3158,19 @@
       <c r="G9" s="22">
         <v>0.70169437000000001</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
       <c r="L9" s="20">
         <v>-22.108287789999999</v>
       </c>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="22">
         <v>0.88935640000000005</v>
       </c>
@@ -2592,17 +3183,17 @@
       <c r="G10" s="22">
         <v>0.50878343999999998</v>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
       <c r="L10" s="20">
         <v>-14.60139663</v>
       </c>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="22">
         <v>0.25094623999999999</v>
       </c>
@@ -2615,17 +3206,17 @@
       <c r="G11" s="22">
         <v>0.49493241999999998</v>
       </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
       <c r="L11" s="20">
         <v>-11.699932459999999</v>
       </c>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="22">
         <v>0.34696206000000002</v>
       </c>
@@ -2638,17 +3229,17 @@
       <c r="G12" s="22">
         <v>0.61302356000000002</v>
       </c>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
       <c r="L12" s="20">
         <v>-16.053765110000001</v>
       </c>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="22">
         <v>0.12487118</v>
       </c>
@@ -2661,17 +3252,17 @@
       <c r="G13" s="22">
         <v>0.2870761</v>
       </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
       <c r="L13" s="20">
         <v>-10.06963343</v>
       </c>
       <c r="M13" s="20"/>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="22">
         <v>0.80130270999999997</v>
       </c>
@@ -2684,17 +3275,17 @@
       <c r="G14" s="22">
         <v>0.19510284</v>
       </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
       <c r="L14" s="20">
         <v>-15.487082539999999</v>
       </c>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="2:16">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="22">
         <v>0.24770826000000001</v>
       </c>
@@ -2707,17 +3298,17 @@
       <c r="G15" s="22">
         <v>0.44132424999999997</v>
       </c>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
       <c r="L15" s="20">
         <v>-12.68168498</v>
       </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="2:16">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="22">
         <v>0.74670223999999996</v>
       </c>
@@ -2730,17 +3321,17 @@
       <c r="G16" s="22">
         <v>0.20656627999999999</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
       <c r="L16" s="20">
         <v>-16.026399770000001</v>
       </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="2:13">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="22">
         <v>0.40066502999999998</v>
       </c>
@@ -2753,17 +3344,17 @@
       <c r="G17" s="22">
         <v>0.24384228999999999</v>
       </c>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
       <c r="L17" s="20">
         <v>-17.049234649999999</v>
       </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="2:13">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="22">
         <v>0.62607060000000003</v>
       </c>
@@ -2776,17 +3367,17 @@
       <c r="G18" s="22">
         <v>0.77885769000000005</v>
       </c>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
       <c r="L18" s="20">
         <v>-12.741765989999999</v>
       </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="2:13">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="22">
         <v>0.95713528999999997</v>
       </c>
@@ -2799,17 +3390,17 @@
       <c r="G19" s="22">
         <v>0.77620990999999995</v>
       </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
       <c r="L19" s="20">
         <v>-27.316396359999999</v>
       </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="2:13">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="22">
         <v>0.73281242999999996</v>
       </c>
@@ -2822,17 +3413,17 @@
       <c r="G20" s="22">
         <v>0.13336572999999999</v>
       </c>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
       <c r="L20" s="20">
         <v>-13.52764887</v>
       </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="2:13">
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="22">
         <v>0.65511547999999997</v>
       </c>
@@ -2845,17 +3436,17 @@
       <c r="G21" s="22">
         <v>8.1516560000000002E-2</v>
       </c>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
       <c r="L21" s="20">
         <v>-16.679115199999998</v>
       </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="2:13">
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="22">
         <v>0.21973443000000001</v>
       </c>
@@ -2868,17 +3459,17 @@
       <c r="G22" s="22">
         <v>8.2569229999999993E-2</v>
       </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
       <c r="L22" s="20">
         <v>-16.507158560000001</v>
       </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="2:13">
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="22">
         <v>0.48859418999999998</v>
       </c>
@@ -2891,17 +3482,17 @@
       <c r="G23" s="22">
         <v>0.37619173</v>
       </c>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
       <c r="L23" s="20">
         <v>-17.81799934</v>
       </c>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="2:13">
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="22">
         <v>0.16713048999999999</v>
       </c>
@@ -2914,17 +3505,17 @@
       <c r="G24" s="22">
         <v>0.95980098000000003</v>
       </c>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
       <c r="L24" s="20">
         <v>-26.561820829999998</v>
       </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="2:13">
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="22">
         <v>0.21691119</v>
       </c>
@@ -2937,17 +3528,17 @@
       <c r="G25" s="22">
         <v>0.77006247999999999</v>
       </c>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
       <c r="L25" s="20">
         <v>-12.75832422</v>
       </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="2:13">
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
       <c r="D26" s="22">
         <v>0.38748783999999997</v>
       </c>
@@ -2960,17 +3551,17 @@
       <c r="G26" s="22">
         <v>0.72382743999999999</v>
       </c>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
       <c r="L26" s="20">
         <v>-19.441557620000001</v>
       </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="2:13">
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
       <c r="D27" s="22">
         <v>0.98562189</v>
       </c>
@@ -2983,17 +3574,17 @@
       <c r="G27" s="22">
         <v>0.85653480000000004</v>
       </c>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
       <c r="L27" s="20">
         <v>-28.903273670000001</v>
       </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="2:13">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="22">
         <v>3.7824829999999997E-2</v>
       </c>
@@ -3006,17 +3597,17 @@
       <c r="G28" s="22">
         <v>0.25392377999999999</v>
       </c>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
       <c r="L28" s="20">
         <v>-13.702746940000001</v>
       </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="2:13">
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
       <c r="D29" s="22">
         <v>0.68348637999999995</v>
       </c>
@@ -3029,17 +3620,17 @@
       <c r="G29" s="22">
         <v>0.99948256000000002</v>
       </c>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
       <c r="L29" s="20">
         <v>-29.427091399999998</v>
       </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="2:13">
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
       <c r="D30" s="22">
         <v>0.17034731</v>
       </c>
@@ -3052,17 +3643,17 @@
       <c r="G30" s="22">
         <v>0.53123149999999997</v>
       </c>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
       <c r="L30" s="20">
         <v>-11.565741989999999</v>
       </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="2:13">
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
       <c r="D31" s="22">
         <v>0.85965692000000005</v>
       </c>
@@ -3075,17 +3666,17 @@
       <c r="G31" s="22">
         <v>9.7796830000000001E-2</v>
       </c>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
       <c r="L31" s="20">
         <v>-26.857786440000002</v>
       </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="2:13">
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="22">
         <v>0.28213837000000003</v>
       </c>
@@ -3098,17 +3689,17 @@
       <c r="G32" s="22">
         <v>9.6301620000000004E-2</v>
       </c>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
       <c r="L32" s="20">
         <v>-7.9667753499999998</v>
       </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="2:16">
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
       <c r="D33" s="22">
         <v>0.32607577999999998</v>
       </c>
@@ -3121,17 +3712,17 @@
       <c r="G33" s="22">
         <v>0.10588734</v>
       </c>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="38"/>
       <c r="L33" s="20">
         <v>-6.7020892500000002</v>
       </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="2:16">
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
       <c r="D34" s="22">
         <v>0.94838935999999996</v>
       </c>
@@ -3144,17 +3735,17 @@
       <c r="G34" s="22">
         <v>0.55219629000000003</v>
       </c>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
       <c r="L34" s="20">
         <v>-32.62566022</v>
       </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="2:16">
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
       <c r="D35" s="22">
         <v>0.66495539000000004</v>
       </c>
@@ -3167,17 +3758,17 @@
       <c r="G35" s="22">
         <v>0.79371778000000004</v>
       </c>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
       <c r="L35" s="20">
         <v>-19.989497929999999</v>
       </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="2:16">
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
       <c r="D36" s="22">
         <v>0.57776561000000004</v>
       </c>
@@ -3190,17 +3781,17 @@
       <c r="G36" s="22">
         <v>0.24900741000000001</v>
       </c>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
       <c r="L36" s="20">
         <v>-4.0255422799999998</v>
       </c>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="2:16">
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
       <c r="D37" s="22">
         <v>0.73861301000000001</v>
       </c>
@@ -3213,17 +3804,17 @@
       <c r="G37" s="22">
         <v>0.50397000999999997</v>
       </c>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
       <c r="L37" s="20">
         <v>-13.12278233</v>
       </c>
       <c r="M37" s="6"/>
     </row>
     <row r="38" spans="2:16">
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
       <c r="D38" s="22">
         <v>0.85481079999999998</v>
       </c>
@@ -3236,9 +3827,9 @@
       <c r="G38" s="22">
         <v>0.80809200999999997</v>
       </c>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
       <c r="L38" s="20">
         <v>-23.1394284</v>
       </c>
@@ -3392,10 +3983,169 @@
       </c>
     </row>
     <row r="45" spans="2:16">
-      <c r="P45" s="2"/>
-    </row>
-    <row r="46" spans="2:16">
-      <c r="P46" s="2"/>
+      <c r="B45" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="23">
+        <v>3</v>
+      </c>
+      <c r="D45" s="27">
+        <v>0.39419710000000002</v>
+      </c>
+      <c r="E45" s="27">
+        <v>0.39469735</v>
+      </c>
+      <c r="F45" s="27">
+        <v>0.39519759999999998</v>
+      </c>
+      <c r="G45" s="27">
+        <v>0.39569785000000002</v>
+      </c>
+      <c r="I45" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="24">
+        <v>3</v>
+      </c>
+      <c r="K45" s="24"/>
+      <c r="L45" s="26">
+        <v>-3.1276999999999999E-2</v>
+      </c>
+      <c r="M45" s="24"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="24"/>
+    </row>
+    <row r="46" spans="2:16" ht="38.1" customHeight="1">
+      <c r="I46" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N46" s="21">
+        <f>MAX(N44,L45)</f>
+        <v>-3.1276999999999999E-2</v>
+      </c>
+      <c r="O46" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="P46" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16">
+      <c r="B47" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="23">
+        <v>4</v>
+      </c>
+      <c r="D47" s="27">
+        <v>0.37218600000000002</v>
+      </c>
+      <c r="E47" s="27">
+        <v>0.37268600000000002</v>
+      </c>
+      <c r="F47" s="27">
+        <v>0.37318699999999999</v>
+      </c>
+      <c r="G47" s="27">
+        <v>0.37368699999999999</v>
+      </c>
+      <c r="I47" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="24">
+        <v>4</v>
+      </c>
+      <c r="K47" s="24"/>
+      <c r="L47" s="26">
+        <v>0.41890036608495901</v>
+      </c>
+      <c r="M47" s="24"/>
+      <c r="N47" s="24"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="24"/>
+    </row>
+    <row r="48" spans="2:16" ht="47.7" customHeight="1">
+      <c r="I48" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N48" s="21">
+        <f>MAX(N46,L47)</f>
+        <v>0.41890036608495901</v>
+      </c>
+      <c r="O48" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="P48" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16">
+      <c r="B49" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="23">
+        <v>5</v>
+      </c>
+      <c r="D49" s="27">
+        <v>0.34817399999999998</v>
+      </c>
+      <c r="E49" s="27">
+        <v>0.34867399999999998</v>
+      </c>
+      <c r="F49" s="27">
+        <v>0.34917399999999998</v>
+      </c>
+      <c r="G49" s="27">
+        <v>0.34967399999999998</v>
+      </c>
+      <c r="I49" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="24">
+        <v>5</v>
+      </c>
+      <c r="K49" s="24"/>
+      <c r="L49" s="26">
+        <v>0.48991130991994303</v>
+      </c>
+      <c r="M49" s="24"/>
+      <c r="N49" s="24"/>
+      <c r="O49" s="24"/>
+      <c r="P49" s="24"/>
+    </row>
+    <row r="50" spans="2:16" ht="38.700000000000003" customHeight="1">
+      <c r="I50" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N50" s="21">
+        <f>MAX(N48,L49)</f>
+        <v>0.48991130991994303</v>
+      </c>
+      <c r="O50" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="P50" s="32" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3414,7 +4164,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB787A30-BB0A-4678-A75A-EF41DE76C694}">
-  <dimension ref="B3:P36"/>
+  <dimension ref="B3:P40"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -3427,43 +4177,43 @@
     <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="10.7890625" customWidth="1"/>
     <col min="14" max="14" width="22.89453125" customWidth="1"/>
-    <col min="15" max="15" width="24.7890625" customWidth="1"/>
+    <col min="15" max="15" width="26.1015625" customWidth="1"/>
     <col min="16" max="16" width="22.15625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:16">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="38.4" customHeight="1">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
       <c r="M7" s="1"/>
       <c r="N7" s="14" t="s">
         <v>6</v>
@@ -3476,8 +4226,8 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="21.3">
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="16" t="s">
         <v>13</v>
       </c>
@@ -3506,10 +4256,10 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="22">
         <v>0.19144707999999999</v>
       </c>
@@ -3522,19 +4272,19 @@
       <c r="G9" s="22">
         <v>0.41458413999999999</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
       <c r="L9" s="20">
         <v>64.443439900000001</v>
       </c>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="22">
         <v>0.75865294999999999</v>
       </c>
@@ -3547,17 +4297,17 @@
       <c r="G10" s="22">
         <v>0.36034155000000001</v>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
       <c r="L10" s="20">
         <v>18.301379600000001</v>
       </c>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="22">
         <v>0.43834986999999997</v>
       </c>
@@ -3570,17 +4320,17 @@
       <c r="G11" s="22">
         <v>0.15129482</v>
       </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
       <c r="L11" s="20">
         <v>0.112939795</v>
       </c>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="22">
         <v>0.70605083000000002</v>
       </c>
@@ -3593,17 +4343,17 @@
       <c r="G12" s="22">
         <v>0.48208754999999998</v>
       </c>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
       <c r="L12" s="20">
         <v>4.2108981300000004</v>
       </c>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="22">
         <v>0.83647799</v>
       </c>
@@ -3616,17 +4366,17 @@
       <c r="G13" s="22">
         <v>0.78564887999999999</v>
       </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
       <c r="L13" s="20">
         <v>258.37052499999999</v>
       </c>
       <c r="M13" s="20"/>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="22">
         <v>0.68343224999999996</v>
       </c>
@@ -3639,17 +4389,17 @@
       <c r="G14" s="22">
         <v>0.56757661000000004</v>
       </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
       <c r="L14" s="20">
         <v>78.434388900000002</v>
       </c>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="2:16">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="22">
         <v>0.55362148</v>
       </c>
@@ -3662,17 +4412,17 @@
       <c r="G15" s="22">
         <v>0.81486974999999995</v>
       </c>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
       <c r="L15" s="20">
         <v>57.571536899999998</v>
       </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="2:16">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="22">
         <v>0.35235627000000003</v>
       </c>
@@ -3685,17 +4435,17 @@
       <c r="G16" s="22">
         <v>0.47311251999999998</v>
       </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
       <c r="L16" s="20">
         <v>109.571876</v>
       </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="2:16">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="22">
         <v>0.15378570999999999</v>
       </c>
@@ -3708,17 +4458,17 @@
       <c r="G17" s="22">
         <v>0.44307416999999999</v>
       </c>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
       <c r="L17" s="20">
         <v>8.8479917599999993</v>
       </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="2:16">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="22">
         <v>0.46344226999999999</v>
       </c>
@@ -3731,17 +4481,17 @@
       <c r="G18" s="22">
         <v>0.95764389999999999</v>
       </c>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
       <c r="L18" s="20">
         <v>233.22361000000001</v>
       </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="2:16">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="22">
         <v>0.67749115000000004</v>
       </c>
@@ -3754,17 +4504,17 @@
       <c r="G19" s="22">
         <v>7.2880479999999997E-2</v>
       </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
       <c r="L19" s="20">
         <v>24.4230883</v>
       </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="2:16">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="22">
         <v>0.58397341000000003</v>
       </c>
@@ -3777,17 +4527,17 @@
       <c r="G20" s="22">
         <v>0.42861464999999999</v>
       </c>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
       <c r="L20" s="20">
         <v>64.420146799999998</v>
       </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="2:16">
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="22">
         <v>0.30688872</v>
       </c>
@@ -3800,17 +4550,17 @@
       <c r="G21" s="22">
         <v>9.5399059999999994E-2</v>
       </c>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
       <c r="L21" s="20">
         <v>63.476715800000001</v>
       </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="2:16">
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="22">
         <v>0.51114177000000005</v>
       </c>
@@ -3823,17 +4573,17 @@
       <c r="G22" s="22">
         <v>0.11235362</v>
       </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
       <c r="L22" s="20">
         <v>79.729129900000004</v>
       </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="2:16">
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="22">
         <v>0.43893337999999998</v>
       </c>
@@ -3846,17 +4596,17 @@
       <c r="G23" s="22">
         <v>0.93369621000000003</v>
       </c>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
       <c r="L23" s="20">
         <v>355.80681800000002</v>
       </c>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="2:16">
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="22">
         <v>0.22418901999999999</v>
       </c>
@@ -3869,17 +4619,17 @@
       <c r="G24" s="22">
         <v>0.87851568000000002</v>
       </c>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
       <c r="L24" s="20">
         <v>1088.8596199999999</v>
       </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="2:16">
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="22">
         <v>0.72526172</v>
       </c>
@@ -3892,17 +4642,17 @@
       <c r="G25" s="22">
         <v>0.75976021999999999</v>
       </c>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
       <c r="L25" s="20">
         <v>28.866751600000001</v>
       </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="2:16">
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
       <c r="D26" s="22">
         <v>0.35548161</v>
       </c>
@@ -3915,17 +4665,17 @@
       <c r="G26" s="22">
         <v>0.12260384000000001</v>
       </c>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
       <c r="L26" s="20">
         <v>45.181570299999997</v>
       </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
       <c r="D27" s="22">
         <v>0.11987923</v>
       </c>
@@ -3938,17 +4688,17 @@
       <c r="G27" s="22">
         <v>0.84980383000000004</v>
       </c>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
       <c r="L27" s="20">
         <v>431.61275699999999</v>
       </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="22">
         <v>0.12688467</v>
       </c>
@@ -3961,9 +4711,9 @@
       <c r="G28" s="22">
         <v>0.19051810999999999</v>
       </c>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
       <c r="L28" s="20">
         <v>9.9723318899999995</v>
       </c>
@@ -4077,7 +4827,7 @@
       <c r="O32" s="24"/>
       <c r="P32" s="24"/>
     </row>
-    <row r="33" spans="9:16" ht="37.200000000000003" customHeight="1">
+    <row r="33" spans="2:16" ht="37.200000000000003" customHeight="1">
       <c r="I33" s="19" t="s">
         <v>7</v>
       </c>
@@ -4098,7 +4848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="9:16" ht="37.5" customHeight="1">
+    <row r="34" spans="2:16" ht="37.5" customHeight="1">
       <c r="I34" s="19" t="s">
         <v>15</v>
       </c>
@@ -4117,11 +4867,158 @@
       </c>
       <c r="P34" s="5"/>
     </row>
-    <row r="35" spans="9:16">
-      <c r="P35" s="2"/>
-    </row>
-    <row r="36" spans="9:16">
-      <c r="P36" s="2"/>
+    <row r="35" spans="2:16">
+      <c r="B35" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="23">
+        <v>3</v>
+      </c>
+      <c r="D35" s="27">
+        <v>0.99849924999999995</v>
+      </c>
+      <c r="E35" s="27">
+        <v>0.99899950000000004</v>
+      </c>
+      <c r="F35" s="27">
+        <v>0.99949975000000002</v>
+      </c>
+      <c r="G35" s="27">
+        <v>1</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="24">
+        <v>3</v>
+      </c>
+      <c r="K35" s="24"/>
+      <c r="L35" s="26">
+        <v>8604.5365110000002</v>
+      </c>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+    </row>
+    <row r="36" spans="2:16" ht="28.8">
+      <c r="I36" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="N36" s="21">
+        <f>MAX(N33,L35)</f>
+        <v>8604.5365110000002</v>
+      </c>
+      <c r="O36" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="P36" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16">
+      <c r="B37" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="23">
+        <v>4</v>
+      </c>
+      <c r="D37" s="27">
+        <v>1</v>
+      </c>
+      <c r="E37" s="27">
+        <v>1</v>
+      </c>
+      <c r="F37" s="27">
+        <v>1</v>
+      </c>
+      <c r="G37" s="27">
+        <v>1</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J37" s="24">
+        <v>4</v>
+      </c>
+      <c r="K37" s="24"/>
+      <c r="L37" s="26">
+        <v>8662.4825000000001</v>
+      </c>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+    </row>
+    <row r="38" spans="2:16" ht="28.8">
+      <c r="I38" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="N38" s="21">
+        <f>MAX(N36,L37)</f>
+        <v>8662.4825000000001</v>
+      </c>
+      <c r="O38" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="P38" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16">
+      <c r="B39" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="23">
+        <v>5</v>
+      </c>
+      <c r="D39" s="27">
+        <v>0.92</v>
+      </c>
+      <c r="E39" s="27">
+        <v>0.92</v>
+      </c>
+      <c r="F39" s="27">
+        <v>0.92</v>
+      </c>
+      <c r="G39" s="27">
+        <v>0.92</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J39" s="24">
+        <v>5</v>
+      </c>
+      <c r="K39" s="24"/>
+      <c r="L39" s="26">
+        <v>4033.8785716173202</v>
+      </c>
+      <c r="M39" s="24"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="24"/>
+    </row>
+    <row r="40" spans="2:16" ht="43.2">
+      <c r="I40" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N40" s="21">
+        <f>MAX(N38,L39)</f>
+        <v>8662.4825000000001</v>
+      </c>
+      <c r="O40" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="P40" s="32" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4140,7 +5037,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B451910E-E097-46FF-B069-9F3B8C7F2915}">
-  <dimension ref="B3:Q38"/>
+  <dimension ref="B3:Q41"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -4158,39 +5055,39 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:17">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:17">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="38.4" customHeight="1">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="J7" s="38" t="s">
+      <c r="J7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
       <c r="N7" s="1"/>
       <c r="O7" s="14" t="s">
         <v>6</v>
@@ -4203,8 +5100,8 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="21.3">
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="16" t="s">
         <v>13</v>
       </c>
@@ -4236,10 +5133,10 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="2:17">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="22">
         <v>0.72818609999999995</v>
       </c>
@@ -4255,19 +5152,19 @@
       <c r="H9" s="22">
         <v>5.6401310000000003E-2</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
       <c r="M9" s="20">
         <v>-0.71426495000000001</v>
       </c>
       <c r="N9" s="4"/>
     </row>
     <row r="10" spans="2:17">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="22">
         <v>0.24238435</v>
       </c>
@@ -4283,17 +5180,17 @@
       <c r="H10" s="22">
         <v>0.50195288999999998</v>
       </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
       <c r="M10" s="20">
         <v>-1.20995524</v>
       </c>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="2:17">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="22">
         <v>0.72952260999999996</v>
       </c>
@@ -4309,17 +5206,17 @@
       <c r="H11" s="22">
         <v>0.67105367999999999</v>
       </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
       <c r="M11" s="20">
         <v>-1.6721999400000001</v>
       </c>
       <c r="N11" s="4"/>
     </row>
     <row r="12" spans="2:17">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="22">
         <v>0.77062023999999996</v>
       </c>
@@ -4335,17 +5232,17 @@
       <c r="H12" s="22">
         <v>0.27354905000000002</v>
       </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
       <c r="M12" s="20">
         <v>-1.5360577099999999</v>
       </c>
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="2:17">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="22">
         <v>0.61881229999999998</v>
       </c>
@@ -4361,17 +5258,17 @@
       <c r="H13" s="22">
         <v>0.32883479999999998</v>
       </c>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
       <c r="M13" s="20">
         <v>-0.82923654999999996</v>
       </c>
       <c r="N13" s="20"/>
     </row>
     <row r="14" spans="2:17">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="22">
         <v>0.78495809000000005</v>
       </c>
@@ -4387,17 +5284,17 @@
       <c r="H14" s="22">
         <v>4.9115000000000001E-3</v>
       </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
       <c r="M14" s="20">
         <v>-1.2470489300000001</v>
       </c>
       <c r="N14" s="4"/>
     </row>
     <row r="15" spans="2:17">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="22">
         <v>0.14511078999999999</v>
       </c>
@@ -4413,17 +5310,17 @@
       <c r="H15" s="22">
         <v>0.23627198999999999</v>
       </c>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
       <c r="M15" s="20">
         <v>-1.23378638</v>
       </c>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="2:17">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="22">
         <v>0.94506906999999996</v>
       </c>
@@ -4439,17 +5336,17 @@
       <c r="H16" s="22">
         <v>0.59801594000000002</v>
       </c>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
       <c r="M16" s="20">
         <v>-1.6943434399999999</v>
       </c>
       <c r="N16" s="6"/>
     </row>
     <row r="17" spans="2:17">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="22">
         <v>0.12572016</v>
       </c>
@@ -4465,17 +5362,17 @@
       <c r="H17" s="22">
         <v>0.75120624000000003</v>
       </c>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
       <c r="M17" s="20">
         <v>-2.57116963</v>
       </c>
       <c r="N17" s="6"/>
     </row>
     <row r="18" spans="2:17">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="22">
         <v>0.75759436000000002</v>
       </c>
@@ -4491,17 +5388,17 @@
       <c r="H18" s="22">
         <v>0.11243304</v>
       </c>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
       <c r="M18" s="20">
         <v>-1.30911635</v>
       </c>
       <c r="N18" s="6"/>
     </row>
     <row r="19" spans="2:17">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="22">
         <v>0.53679690000000002</v>
       </c>
@@ -4517,17 +5414,17 @@
       <c r="H19" s="22">
         <v>0.52252829999999995</v>
       </c>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
       <c r="M19" s="20">
         <v>-1.14478485</v>
       </c>
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="2:17">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="22">
         <v>0.95773967000000004</v>
       </c>
@@ -4543,17 +5440,17 @@
       <c r="H20" s="22">
         <v>7.1317370000000005E-2</v>
       </c>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
       <c r="M20" s="20">
         <v>-1.91267714</v>
       </c>
       <c r="N20" s="6"/>
     </row>
     <row r="21" spans="2:17">
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="22">
         <v>0.62930790000000003</v>
       </c>
@@ -4569,17 +5466,17 @@
       <c r="H21" s="22">
         <v>0.11062445999999999</v>
       </c>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
       <c r="M21" s="20">
         <v>-1.62283895</v>
       </c>
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="2:17">
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="22">
         <v>2.1735310000000001E-2</v>
       </c>
@@ -4595,17 +5492,17 @@
       <c r="H22" s="22">
         <v>0.51108173000000001</v>
       </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
       <c r="M22" s="20">
         <v>-1.3566821099999999</v>
       </c>
       <c r="N22" s="6"/>
     </row>
     <row r="23" spans="2:17">
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="22">
         <v>0.43934425999999999</v>
       </c>
@@ -4621,17 +5518,17 @@
       <c r="H23" s="22">
         <v>0.87788847000000003</v>
       </c>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
       <c r="M23" s="20">
         <v>-2.0184253999999999</v>
       </c>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="2:17">
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="22">
         <v>0.25890556999999997</v>
       </c>
@@ -4647,17 +5544,17 @@
       <c r="H24" s="22">
         <v>0.59310317999999995</v>
       </c>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
       <c r="M24" s="20">
         <v>-1.7025578400000001</v>
       </c>
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="2:17">
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="22">
         <v>0.43216592999999998</v>
       </c>
@@ -4673,17 +5570,17 @@
       <c r="H25" s="22">
         <v>0.61496183999999998</v>
       </c>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
       <c r="M25" s="20">
         <v>-1.2942469599999999</v>
       </c>
       <c r="N25" s="6"/>
     </row>
     <row r="26" spans="2:17">
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
       <c r="D26" s="22">
         <v>0.78287982</v>
       </c>
@@ -4699,17 +5596,17 @@
       <c r="H26" s="22">
         <v>1.032599E-2</v>
       </c>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
       <c r="M26" s="20">
         <v>-0.93575655999999996</v>
       </c>
       <c r="N26" s="6"/>
     </row>
     <row r="27" spans="2:17">
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
       <c r="D27" s="22">
         <v>0.92177620000000005</v>
       </c>
@@ -4725,17 +5622,17 @@
       <c r="H27" s="22">
         <v>0.73562569</v>
       </c>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
       <c r="M27" s="20">
         <v>-2.1557677599999998</v>
       </c>
       <c r="N27" s="6"/>
     </row>
     <row r="28" spans="2:17">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="22">
         <v>0.12667892</v>
       </c>
@@ -4751,9 +5648,9 @@
       <c r="H28" s="22">
         <v>0.89281918999999998</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
       <c r="M28" s="20">
         <v>-1.7468820899999999</v>
       </c>
@@ -4873,7 +5770,7 @@
       <c r="P32" s="24"/>
       <c r="Q32" s="24"/>
     </row>
-    <row r="33" spans="10:17" ht="45.3" customHeight="1">
+    <row r="33" spans="2:17" ht="45.3" customHeight="1">
       <c r="J33" s="19" t="s">
         <v>7</v>
       </c>
@@ -4894,7 +5791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="10:17" ht="54.6" customHeight="1">
+    <row r="34" spans="2:17" ht="54.6" customHeight="1">
       <c r="J34" s="19" t="s">
         <v>15</v>
       </c>
@@ -4913,14 +5810,191 @@
       </c>
       <c r="Q34" s="5"/>
     </row>
-    <row r="35" spans="10:17">
-      <c r="Q35" s="2"/>
-    </row>
-    <row r="36" spans="10:17">
-      <c r="Q36" s="2"/>
-    </row>
-    <row r="38" spans="10:17">
-      <c r="M38" s="21"/>
+    <row r="35" spans="2:17">
+      <c r="B35" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="23">
+        <v>3</v>
+      </c>
+      <c r="D35" s="27">
+        <v>0.368147</v>
+      </c>
+      <c r="E35" s="27">
+        <v>0.36854700000000001</v>
+      </c>
+      <c r="F35" s="27">
+        <v>0.368948</v>
+      </c>
+      <c r="G35" s="27">
+        <v>0.36934800000000001</v>
+      </c>
+      <c r="H35" s="27">
+        <v>0.36974800000000002</v>
+      </c>
+      <c r="J35" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="24">
+        <v>3</v>
+      </c>
+      <c r="L35" s="24"/>
+      <c r="M35" s="26">
+        <v>-0.97338260744508798</v>
+      </c>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+    </row>
+    <row r="36" spans="2:17" ht="50.4" customHeight="1">
+      <c r="J36" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O36" s="21">
+        <f>MAX(O33,M35)</f>
+        <v>-0.71426495000000001</v>
+      </c>
+      <c r="P36" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q36" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" ht="43.2">
+      <c r="J37" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O37" s="21">
+        <f>MAX(O33,M35)</f>
+        <v>-0.71426495000000001</v>
+      </c>
+      <c r="P37" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17">
+      <c r="B38" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="23">
+        <v>4</v>
+      </c>
+      <c r="D38" s="27">
+        <v>0.41816700000000001</v>
+      </c>
+      <c r="E38" s="27">
+        <v>0.41856700000000002</v>
+      </c>
+      <c r="F38" s="27">
+        <v>0.41896800000000001</v>
+      </c>
+      <c r="G38" s="27">
+        <v>0.41936800000000002</v>
+      </c>
+      <c r="H38" s="27">
+        <v>0.41976799999999997</v>
+      </c>
+      <c r="J38" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" s="24">
+        <v>4</v>
+      </c>
+      <c r="L38" s="24"/>
+      <c r="M38" s="26">
+        <v>-0.91183308716006894</v>
+      </c>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
+    </row>
+    <row r="39" spans="2:17" ht="43.2">
+      <c r="J39" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O39" s="21">
+        <f>MAX(O36,M38)</f>
+        <v>-0.71426495000000001</v>
+      </c>
+      <c r="P39" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17">
+      <c r="B40" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="23">
+        <v>5</v>
+      </c>
+      <c r="D40" s="27">
+        <v>0.99839900000000004</v>
+      </c>
+      <c r="E40" s="27">
+        <v>0.99879899999999999</v>
+      </c>
+      <c r="F40" s="27">
+        <v>0.99919899999999995</v>
+      </c>
+      <c r="G40" s="27">
+        <v>0.99959900000000002</v>
+      </c>
+      <c r="H40" s="27">
+        <v>1</v>
+      </c>
+      <c r="J40" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="K40" s="24">
+        <v>5</v>
+      </c>
+      <c r="L40" s="24"/>
+      <c r="M40" s="26">
+        <v>-2.7014287206272001</v>
+      </c>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+    </row>
+    <row r="41" spans="2:17" ht="43.2">
+      <c r="J41" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="O41" s="21">
+        <f>MAX(O39,M40)</f>
+        <v>-0.71426495000000001</v>
+      </c>
+      <c r="P41" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q41" s="32" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4939,7 +6013,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B58C19-2A2F-49AE-AB19-E8DF9CAE3947}">
-  <dimension ref="B3:R46"/>
+  <dimension ref="B3:R50"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -4957,40 +6031,40 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:18">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="11">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="38.4" customHeight="1">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="K7" s="38" t="s">
+      <c r="K7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
       <c r="O7" s="1"/>
       <c r="P7" s="14" t="s">
         <v>6</v>
@@ -5003,8 +6077,8 @@
       </c>
     </row>
     <row r="8" spans="2:18" ht="21.3">
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="16" t="s">
         <v>13</v>
       </c>
@@ -5039,10 +6113,10 @@
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="2:18">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="22">
         <v>0.27262382000000002</v>
       </c>
@@ -5061,19 +6135,19 @@
       <c r="I9" s="22">
         <v>0.79586361999999999</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="K9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
       <c r="N9" s="20">
         <v>0.60443270000000004</v>
       </c>
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="2:18">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="22">
         <v>0.54300258000000001</v>
       </c>
@@ -5092,17 +6166,17 @@
       <c r="I10" s="22">
         <v>0.34313265999999998</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
       <c r="N10" s="20">
         <v>0.56275306999999997</v>
       </c>
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="2:18">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="22">
         <v>9.0832250000000003E-2</v>
       </c>
@@ -5121,17 +6195,17 @@
       <c r="I11" s="22">
         <v>0.64026539999999998</v>
       </c>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
       <c r="N11" s="20">
         <v>7.5032400000000004E-3</v>
       </c>
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="2:18">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="22">
         <v>0.11886697</v>
       </c>
@@ -5150,17 +6224,17 @@
       <c r="I12" s="22">
         <v>0.58523563000000001</v>
       </c>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
       <c r="N12" s="20">
         <v>6.1424300000000001E-2</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="2:18">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="22">
         <v>0.63021764000000002</v>
       </c>
@@ -5179,17 +6253,17 @@
       <c r="I13" s="22">
         <v>0.34842920999999999</v>
       </c>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
       <c r="N13" s="20">
         <v>0.27304679999999998</v>
       </c>
       <c r="O13" s="20"/>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="22">
         <v>0.76491916999999998</v>
       </c>
@@ -5208,17 +6282,17 @@
       <c r="I14" s="22">
         <v>9.5793660000000003E-2</v>
       </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
       <c r="N14" s="20">
         <v>8.3746570000000006E-2</v>
       </c>
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="2:18">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="22">
         <v>5.7895540000000002E-2</v>
       </c>
@@ -5237,17 +6311,17 @@
       <c r="I15" s="22">
         <v>0.73096983999999998</v>
       </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
       <c r="N15" s="20">
         <v>1.3649682999999999</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="2:18">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="22">
         <v>0.19525187999999999</v>
       </c>
@@ -5266,17 +6340,17 @@
       <c r="I16" s="22">
         <v>0.10703171</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
       <c r="N16" s="20">
         <v>9.2644950000000004E-2</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="2:15">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="22">
         <v>0.64230297999999997</v>
       </c>
@@ -5295,17 +6369,17 @@
       <c r="I17" s="22">
         <v>0.69241640000000004</v>
       </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
       <c r="N17" s="20">
         <v>1.7869599999999999E-2</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="2:15">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="22">
         <v>0.78994255000000002</v>
       </c>
@@ -5324,17 +6398,17 @@
       <c r="I18" s="22">
         <v>5.1099859999999997E-2</v>
       </c>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
       <c r="N18" s="20">
         <v>3.3564940000000001E-2</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="2:15">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="22">
         <v>0.52849732999999999</v>
       </c>
@@ -5353,17 +6427,17 @@
       <c r="I19" s="22">
         <v>0.63747637000000001</v>
       </c>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
       <c r="N19" s="20">
         <v>7.3516300000000007E-2</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="2:15">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="22">
         <v>0.72261522</v>
       </c>
@@ -5382,17 +6456,17 @@
       <c r="I20" s="22">
         <v>0.35995166000000001</v>
       </c>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
       <c r="N20" s="20">
         <v>0.20630970000000001</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="22">
         <v>7.5664919999999997E-2</v>
       </c>
@@ -5411,17 +6485,17 @@
       <c r="I21" s="22">
         <v>0.82233078999999998</v>
       </c>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
       <c r="N21" s="20">
         <v>8.8256299999999992E-3</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="22">
         <v>0.94245084000000001</v>
       </c>
@@ -5440,17 +6514,17 @@
       <c r="I22" s="22">
         <v>0.71195755000000005</v>
       </c>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
       <c r="N22" s="20">
         <v>0.26840032000000003</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="22">
         <v>0.14864701999999999</v>
       </c>
@@ -5469,17 +6543,17 @@
       <c r="I23" s="22">
         <v>0.51691776</v>
       </c>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
       <c r="N23" s="20">
         <v>0.61152552999999998</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="2:15">
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="22">
         <v>0.81711239000000002</v>
       </c>
@@ -5498,17 +6572,17 @@
       <c r="I24" s="22">
         <v>0.44967361</v>
       </c>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
       <c r="N24" s="20">
         <v>1.4798179999999999E-2</v>
       </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="22">
         <v>0.41762629000000001</v>
       </c>
@@ -5527,17 +6601,17 @@
       <c r="I25" s="22">
         <v>0.25464091999999999</v>
       </c>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
       <c r="N25" s="20">
         <v>0.27489250999999998</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="2:15">
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
       <c r="D26" s="22">
         <v>0.72628566000000006</v>
       </c>
@@ -5556,17 +6630,17 @@
       <c r="I26" s="22">
         <v>0.14341787</v>
       </c>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
       <c r="N26" s="20">
         <v>6.6763249999999996E-2</v>
       </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="2:15">
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
       <c r="D27" s="22">
         <v>0.31981042999999998</v>
       </c>
@@ -5585,17 +6659,17 @@
       <c r="I27" s="22">
         <v>0.61908249999999998</v>
       </c>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
       <c r="N27" s="20">
         <v>4.2118349999999999E-2</v>
       </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="2:15">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="22">
         <v>0.87987128000000003</v>
       </c>
@@ -5614,17 +6688,17 @@
       <c r="I28" s="22">
         <v>0.11486924</v>
       </c>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
       <c r="N28" s="20">
         <v>2.7014700000000001E-3</v>
       </c>
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="2:15">
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
       <c r="D29" s="22">
         <v>0.54124077999999998</v>
       </c>
@@ -5643,17 +6717,17 @@
       <c r="I29" s="22">
         <v>0.63370428999999995</v>
       </c>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
       <c r="N29" s="20">
         <v>1.8209070000000001E-2</v>
       </c>
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="2:15">
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
       <c r="D30" s="22">
         <v>0.22634792000000001</v>
       </c>
@@ -5672,17 +6746,17 @@
       <c r="I30" s="22">
         <v>0.95101391999999996</v>
       </c>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
       <c r="N30" s="20">
         <v>7.0160300000000004E-3</v>
       </c>
       <c r="O30" s="6"/>
     </row>
     <row r="31" spans="2:15">
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
       <c r="D31" s="22">
         <v>0.68685257</v>
       </c>
@@ -5701,17 +6775,17 @@
       <c r="I31" s="22">
         <v>0.65554290000000004</v>
       </c>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
       <c r="N31" s="20">
         <v>0.10050661</v>
       </c>
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="2:15">
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="22">
         <v>0.17597753999999999</v>
       </c>
@@ -5730,17 +6804,17 @@
       <c r="I32" s="22">
         <v>0.72814108</v>
       </c>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
       <c r="N32" s="20">
         <v>0.47539552000000002</v>
       </c>
       <c r="O32" s="6"/>
     </row>
     <row r="33" spans="2:18">
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
       <c r="D33" s="22">
         <v>0.88164673999999998</v>
       </c>
@@ -5759,17 +6833,17 @@
       <c r="I33" s="22">
         <v>0.73066019000000004</v>
       </c>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
       <c r="N33" s="20">
         <v>0.67514163000000005</v>
       </c>
       <c r="O33" s="6"/>
     </row>
     <row r="34" spans="2:18">
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
       <c r="D34" s="22">
         <v>6.6610509999999998E-2</v>
       </c>
@@ -5788,17 +6862,17 @@
       <c r="I34" s="22">
         <v>0.77778822000000003</v>
       </c>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
       <c r="N34" s="20">
         <v>0.51645722000000005</v>
       </c>
       <c r="O34" s="6"/>
     </row>
     <row r="35" spans="2:18">
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
       <c r="D35" s="22">
         <v>0.93246638000000004</v>
       </c>
@@ -5817,17 +6891,17 @@
       <c r="I35" s="22">
         <v>0.51985176</v>
       </c>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
       <c r="N35" s="20">
         <v>3.7774800000000002E-3</v>
       </c>
       <c r="O35" s="6"/>
     </row>
     <row r="36" spans="2:18">
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
       <c r="D36" s="22">
         <v>0.84686697</v>
       </c>
@@ -5846,17 +6920,17 @@
       <c r="I36" s="22">
         <v>8.1306089999999998E-2</v>
       </c>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
       <c r="N36" s="20">
         <v>3.1343299999999998E-3</v>
       </c>
       <c r="O36" s="6"/>
     </row>
     <row r="37" spans="2:18">
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
       <c r="D37" s="22">
         <v>0.80628208000000001</v>
       </c>
@@ -5875,17 +6949,17 @@
       <c r="I37" s="22">
         <v>0.36288397999999999</v>
       </c>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
       <c r="N37" s="20">
         <v>2.134252E-2</v>
       </c>
       <c r="O37" s="6"/>
     </row>
     <row r="38" spans="2:18">
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
       <c r="D38" s="22">
         <v>0.47682312999999998</v>
       </c>
@@ -5904,9 +6978,9 @@
       <c r="I38" s="22">
         <v>7.9664020000000002E-2</v>
       </c>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
       <c r="N38" s="20">
         <v>9.5411159999999995E-2</v>
       </c>
@@ -6073,10 +7147,169 @@
       <c r="R44" s="5"/>
     </row>
     <row r="45" spans="2:18">
-      <c r="R45" s="2"/>
-    </row>
-    <row r="46" spans="2:18">
-      <c r="R46" s="2"/>
+      <c r="B45" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="23">
+        <v>3</v>
+      </c>
+      <c r="D45" s="27">
+        <v>0.99833300000000003</v>
+      </c>
+      <c r="E45" s="27">
+        <v>0.99866600000000005</v>
+      </c>
+      <c r="F45" s="27">
+        <v>0.999</v>
+      </c>
+      <c r="G45" s="27">
+        <v>0.99933300000000003</v>
+      </c>
+      <c r="H45" s="27">
+        <v>0.99966699999999997</v>
+      </c>
+      <c r="I45" s="27">
+        <v>1</v>
+      </c>
+      <c r="K45" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="24">
+        <v>3</v>
+      </c>
+      <c r="M45" s="24"/>
+      <c r="N45" s="26">
+        <v>3.4997016155550602E-5</v>
+      </c>
+      <c r="O45" s="24"/>
+      <c r="P45" s="24"/>
+      <c r="Q45" s="24"/>
+      <c r="R45" s="24"/>
+    </row>
+    <row r="46" spans="2:18" ht="43.2">
+      <c r="K46" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="P46" s="21">
+        <f>MAX(P43,N45)</f>
+        <v>1.3649682999999999</v>
+      </c>
+      <c r="Q46" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="R46" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18">
+      <c r="B47" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="23">
+        <v>4</v>
+      </c>
+      <c r="D47" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="E47" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="F47" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="G47" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="H47" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="I47" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="K47" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="24">
+        <v>4</v>
+      </c>
+      <c r="M47" s="24"/>
+      <c r="N47" s="26">
+        <v>1.8037650755561301</v>
+      </c>
+      <c r="O47" s="24"/>
+      <c r="P47" s="24"/>
+      <c r="Q47" s="24"/>
+      <c r="R47" s="24"/>
+    </row>
+    <row r="48" spans="2:18" ht="43.2">
+      <c r="K48" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="P48" s="21">
+        <f>MAX(P46,N47)</f>
+        <v>1.8037650755561301</v>
+      </c>
+      <c r="Q48" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="R48" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18">
+      <c r="B49" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="23">
+        <v>5</v>
+      </c>
+      <c r="D49" s="27">
+        <v>0.25408399999999998</v>
+      </c>
+      <c r="E49" s="27">
+        <v>0.25441799999999998</v>
+      </c>
+      <c r="F49" s="27">
+        <v>0.25475100000000001</v>
+      </c>
+      <c r="G49" s="27">
+        <v>0.25508500000000001</v>
+      </c>
+      <c r="H49" s="27">
+        <v>0.25541799999999998</v>
+      </c>
+      <c r="I49" s="27">
+        <v>0.25575100000000001</v>
+      </c>
+      <c r="K49" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="L49" s="24">
+        <v>5</v>
+      </c>
+      <c r="M49" s="24"/>
+      <c r="N49" s="26">
+        <v>0.753853836248642</v>
+      </c>
+      <c r="O49" s="24"/>
+      <c r="P49" s="24"/>
+      <c r="Q49" s="24"/>
+      <c r="R49" s="24"/>
+    </row>
+    <row r="50" spans="2:18" ht="43.2">
+      <c r="K50" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="P50" s="21">
+        <f>MAX(P48,N49)</f>
+        <v>1.8037650755561301</v>
+      </c>
+      <c r="Q50" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="R50" s="29" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6095,13 +7328,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0AA28BB-74D8-433B-A00A-14B553BBFF2F}">
-  <dimension ref="B3:T56"/>
+  <dimension ref="B3:T61"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
     <col min="3" max="3" width="12.05078125" customWidth="1"/>
     <col min="4" max="4" width="11.62890625" customWidth="1"/>
-    <col min="5" max="11" width="11.89453125" customWidth="1"/>
+    <col min="5" max="5" width="13.62890625" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="11.89453125" customWidth="1"/>
     <col min="13" max="13" width="26.5234375" customWidth="1"/>
     <col min="14" max="14" width="17.15625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.15625" customWidth="1"/>
@@ -6113,42 +7347,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:20">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="11">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:20">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="38.4" customHeight="1">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="M7" s="38" t="s">
+      <c r="M7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="14" t="s">
         <v>6</v>
@@ -6161,8 +7395,8 @@
       </c>
     </row>
     <row r="8" spans="2:20" ht="21.3">
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="16" t="s">
         <v>13</v>
       </c>
@@ -6203,10 +7437,10 @@
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="2:20">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="22">
         <v>0.60499444999999996</v>
       </c>
@@ -6231,19 +7465,19 @@
       <c r="K9" s="22">
         <v>0.73428137999999998</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="M9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
       <c r="P9" s="20">
         <v>7.3987211000000004</v>
       </c>
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="2:20">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="22">
         <v>0.17800695999999999</v>
       </c>
@@ -6268,17 +7502,17 @@
       <c r="K10" s="22">
         <v>0.10713163000000001</v>
       </c>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
       <c r="P10" s="20">
         <v>7.0052273600000001</v>
       </c>
       <c r="Q10" s="4"/>
     </row>
     <row r="11" spans="2:20">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="22">
         <v>9.0769800000000001E-3</v>
       </c>
@@ -6303,17 +7537,17 @@
       <c r="K11" s="22">
         <v>0.36732026000000001</v>
       </c>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
       <c r="P11" s="20">
         <v>8.45948162</v>
       </c>
       <c r="Q11" s="4"/>
     </row>
     <row r="12" spans="2:20">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="22">
         <v>0.50602815999999995</v>
       </c>
@@ -6338,17 +7572,17 @@
       <c r="K12" s="22">
         <v>0.29247234</v>
       </c>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
-      <c r="O12" s="32"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
       <c r="P12" s="20">
         <v>8.2840078100000003</v>
       </c>
       <c r="Q12" s="6"/>
     </row>
     <row r="13" spans="2:20">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="22">
         <v>0.35990926000000001</v>
       </c>
@@ -6373,17 +7607,17 @@
       <c r="K13" s="22">
         <v>0.59388173</v>
       </c>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
       <c r="P13" s="20">
         <v>8.6061167899999997</v>
       </c>
       <c r="Q13" s="20"/>
     </row>
     <row r="14" spans="2:20">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="22">
         <v>0.77881834000000005</v>
       </c>
@@ -6408,17 +7642,17 @@
       <c r="K14" s="22">
         <v>0.66003208999999996</v>
       </c>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="32"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
       <c r="P14" s="20">
         <v>8.5417479200000006</v>
       </c>
       <c r="Q14" s="4"/>
     </row>
     <row r="15" spans="2:20">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="22">
         <v>0.90864931999999998</v>
       </c>
@@ -6443,17 +7677,17 @@
       <c r="K15" s="22">
         <v>0.74249593999999997</v>
       </c>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
       <c r="P15" s="20">
         <v>7.3274345800000003</v>
       </c>
       <c r="Q15" s="6"/>
     </row>
     <row r="16" spans="2:20">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="22">
         <v>0.58637143999999997</v>
       </c>
@@ -6478,17 +7712,17 @@
       <c r="K16" s="22">
         <v>9.7915619999999995E-2</v>
       </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
       <c r="P16" s="20">
         <v>7.2998720500000003</v>
       </c>
       <c r="Q16" s="6"/>
     </row>
     <row r="17" spans="2:17">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="22">
         <v>0.76113732999999995</v>
       </c>
@@ -6513,17 +7747,17 @@
       <c r="K17" s="22">
         <v>4.1956069999999998E-2</v>
       </c>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
       <c r="P17" s="20">
         <v>7.9578747400000003</v>
       </c>
       <c r="Q17" s="6"/>
     </row>
     <row r="18" spans="2:17">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="22">
         <v>0.98493319999999995</v>
       </c>
@@ -6548,17 +7782,17 @@
       <c r="K18" s="22">
         <v>0.31368272000000003</v>
       </c>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
       <c r="P18" s="20">
         <v>5.5921933900000003</v>
       </c>
       <c r="Q18" s="6"/>
     </row>
     <row r="19" spans="2:17">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="22">
         <v>0.11207130999999999</v>
       </c>
@@ -6583,17 +7817,17 @@
       <c r="K19" s="22">
         <v>0.67475275999999995</v>
       </c>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
       <c r="P19" s="20">
         <v>7.8545409900000003</v>
       </c>
       <c r="Q19" s="6"/>
     </row>
     <row r="20" spans="2:17">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="22">
         <v>0.79188751000000002</v>
       </c>
@@ -6618,17 +7852,17 @@
       <c r="K20" s="22">
         <v>0.62532792000000004</v>
       </c>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
       <c r="P20" s="20">
         <v>6.7919857800000001</v>
       </c>
       <c r="Q20" s="6"/>
     </row>
     <row r="21" spans="2:17">
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="22">
         <v>0.14355029999999999</v>
       </c>
@@ -6653,17 +7887,17 @@
       <c r="K21" s="22">
         <v>0.20584079999999999</v>
       </c>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
       <c r="P21" s="20">
         <v>8.97655402</v>
       </c>
       <c r="Q21" s="6"/>
     </row>
     <row r="22" spans="2:17">
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="22">
         <v>0.76991655000000003</v>
       </c>
@@ -6688,17 +7922,17 @@
       <c r="K22" s="22">
         <v>0.66313109000000003</v>
       </c>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
       <c r="P22" s="20">
         <v>7.3790829000000002</v>
       </c>
       <c r="Q22" s="6"/>
     </row>
     <row r="23" spans="2:17">
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="22">
         <v>5.6447410000000003E-2</v>
       </c>
@@ -6723,17 +7957,17 @@
       <c r="K23" s="22">
         <v>0.89308498000000003</v>
       </c>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
       <c r="P23" s="20">
         <v>9.5984820000000006</v>
       </c>
       <c r="Q23" s="6"/>
     </row>
     <row r="24" spans="2:17">
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="22">
         <v>0.86243745000000005</v>
       </c>
@@ -6758,17 +7992,17 @@
       <c r="K24" s="22">
         <v>0.47646168999999999</v>
       </c>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
       <c r="P24" s="20">
         <v>8.1599831900000002</v>
       </c>
       <c r="Q24" s="6"/>
     </row>
     <row r="25" spans="2:17">
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="22">
         <v>0.35151189999999999</v>
       </c>
@@ -6793,17 +8027,17 @@
       <c r="K25" s="22">
         <v>0.19572429</v>
       </c>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
       <c r="P25" s="20">
         <v>7.1316239699999997</v>
       </c>
       <c r="Q25" s="6"/>
     </row>
     <row r="26" spans="2:17">
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
       <c r="D26" s="22">
         <v>0.73590363999999997</v>
       </c>
@@ -6828,17 +8062,17 @@
       <c r="K26" s="22">
         <v>0.37433978000000001</v>
       </c>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
       <c r="P26" s="20">
         <v>6.7679625300000001</v>
       </c>
       <c r="Q26" s="6"/>
     </row>
     <row r="27" spans="2:17">
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
       <c r="D27" s="22">
         <v>0.68029397000000003</v>
       </c>
@@ -6863,17 +8097,17 @@
       <c r="K27" s="22">
         <v>0.36420013000000001</v>
       </c>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
       <c r="P27" s="20">
         <v>7.4337440700000004</v>
       </c>
       <c r="Q27" s="6"/>
     </row>
     <row r="28" spans="2:17">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="22">
         <v>4.4329250000000001E-2</v>
       </c>
@@ -6898,17 +8132,17 @@
       <c r="K28" s="22">
         <v>7.7952930000000004E-2</v>
       </c>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
       <c r="P28" s="20">
         <v>9.0130751500000006</v>
       </c>
       <c r="Q28" s="6"/>
     </row>
     <row r="29" spans="2:17">
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
       <c r="D29" s="22">
         <v>0.77834548000000003</v>
       </c>
@@ -6933,17 +8167,17 @@
       <c r="K29" s="22">
         <v>0.9887551</v>
       </c>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="32"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
       <c r="P29" s="20">
         <v>7.3108938200000004</v>
       </c>
       <c r="Q29" s="6"/>
     </row>
     <row r="30" spans="2:17">
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
       <c r="D30" s="22">
         <v>0.89888710999999999</v>
       </c>
@@ -6968,17 +8202,17 @@
       <c r="K30" s="22">
         <v>0.47239821999999998</v>
       </c>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
-      <c r="O30" s="32"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
       <c r="P30" s="20">
         <v>5.8410673099999997</v>
       </c>
       <c r="Q30" s="6"/>
     </row>
     <row r="31" spans="2:17">
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
       <c r="D31" s="22">
         <v>0.14512029000000001</v>
       </c>
@@ -7003,17 +8237,17 @@
       <c r="K31" s="22">
         <v>0.72861058000000001</v>
       </c>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
       <c r="P31" s="20">
         <v>9.1416394899999993</v>
       </c>
       <c r="Q31" s="6"/>
     </row>
     <row r="32" spans="2:17">
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="22">
         <v>0.33895441999999998</v>
       </c>
@@ -7038,17 +8272,17 @@
       <c r="K32" s="22">
         <v>0.73215346999999997</v>
       </c>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
       <c r="P32" s="20">
         <v>8.8175584400000009</v>
       </c>
       <c r="Q32" s="6"/>
     </row>
     <row r="33" spans="2:17">
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
       <c r="D33" s="22">
         <v>0.17615001999999999</v>
       </c>
@@ -7073,17 +8307,17 @@
       <c r="K33" s="22">
         <v>0.59589758000000004</v>
       </c>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
       <c r="P33" s="20">
         <v>6.4519431300000001</v>
       </c>
       <c r="Q33" s="6"/>
     </row>
     <row r="34" spans="2:17">
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
       <c r="D34" s="22">
         <v>2.8946630000000001E-2</v>
       </c>
@@ -7108,17 +8342,17 @@
       <c r="K34" s="22">
         <v>0.52488504999999996</v>
       </c>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-      <c r="O34" s="32"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
       <c r="P34" s="20">
         <v>8.8307450500000009</v>
       </c>
       <c r="Q34" s="6"/>
     </row>
     <row r="35" spans="2:17">
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
       <c r="D35" s="22">
         <v>0.19263986999999999</v>
       </c>
@@ -7143,17 +8377,17 @@
       <c r="K35" s="22">
         <v>0.29551759</v>
       </c>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
       <c r="P35" s="20">
         <v>9.3442742800000005</v>
       </c>
       <c r="Q35" s="6"/>
     </row>
     <row r="36" spans="2:17">
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
       <c r="D36" s="22">
         <v>0.94318502000000004</v>
       </c>
@@ -7178,17 +8412,17 @@
       <c r="K36" s="22">
         <v>0.96009372000000004</v>
       </c>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
-      <c r="O36" s="32"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
       <c r="P36" s="20">
         <v>6.88784639</v>
       </c>
       <c r="Q36" s="6"/>
     </row>
     <row r="37" spans="2:17">
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
       <c r="D37" s="22">
         <v>0.53272140000000001</v>
       </c>
@@ -7213,17 +8447,17 @@
       <c r="K37" s="22">
         <v>0.12790199999999999</v>
       </c>
-      <c r="M37" s="32"/>
-      <c r="N37" s="32"/>
-      <c r="O37" s="32"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="38"/>
       <c r="P37" s="20">
         <v>8.0422125399999995</v>
       </c>
       <c r="Q37" s="6"/>
     </row>
     <row r="38" spans="2:17">
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
       <c r="D38" s="22">
         <v>0.44709584000000002</v>
       </c>
@@ -7248,17 +8482,17 @@
       <c r="K38" s="22">
         <v>0.44683846999999999</v>
       </c>
-      <c r="M38" s="32"/>
-      <c r="N38" s="32"/>
-      <c r="O38" s="32"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
       <c r="P38" s="20">
         <v>7.6923680499999998</v>
       </c>
       <c r="Q38" s="6"/>
     </row>
     <row r="39" spans="2:17">
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
       <c r="D39" s="22">
         <v>0.38222497</v>
       </c>
@@ -7283,17 +8517,17 @@
       <c r="K39" s="22">
         <v>0.76863196</v>
       </c>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-      <c r="O39" s="32"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="38"/>
       <c r="P39" s="20">
         <v>7.9237587700000001</v>
       </c>
       <c r="Q39" s="6"/>
     </row>
     <row r="40" spans="2:17">
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
       <c r="D40" s="22">
         <v>0.53281953000000004</v>
       </c>
@@ -7318,17 +8552,17 @@
       <c r="K40" s="22">
         <v>0.52534791000000003</v>
       </c>
-      <c r="M40" s="32"/>
-      <c r="N40" s="32"/>
-      <c r="O40" s="32"/>
+      <c r="M40" s="38"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="38"/>
       <c r="P40" s="20">
         <v>8.4217592400000001</v>
       </c>
       <c r="Q40" s="6"/>
     </row>
     <row r="41" spans="2:17">
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
       <c r="D41" s="22">
         <v>0.39486518999999998</v>
       </c>
@@ -7353,17 +8587,17 @@
       <c r="K41" s="22">
         <v>0.87114550999999996</v>
       </c>
-      <c r="M41" s="32"/>
-      <c r="N41" s="32"/>
-      <c r="O41" s="32"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
       <c r="P41" s="20">
         <v>8.2780623999999996</v>
       </c>
       <c r="Q41" s="6"/>
     </row>
     <row r="42" spans="2:17">
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
       <c r="D42" s="22">
         <v>0.98594539000000003</v>
       </c>
@@ -7388,17 +8622,17 @@
       <c r="K42" s="22">
         <v>0.10336036</v>
       </c>
-      <c r="M42" s="32"/>
-      <c r="N42" s="32"/>
-      <c r="O42" s="32"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
       <c r="P42" s="20">
         <v>7.1134571600000003</v>
       </c>
       <c r="Q42" s="6"/>
     </row>
     <row r="43" spans="2:17">
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
       <c r="D43" s="22">
         <v>0.96457338999999997</v>
       </c>
@@ -7423,17 +8657,17 @@
       <c r="K43" s="22">
         <v>0.56091749999999996</v>
       </c>
-      <c r="M43" s="32"/>
-      <c r="N43" s="32"/>
-      <c r="O43" s="32"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
       <c r="P43" s="20">
         <v>6.4025884099999999</v>
       </c>
       <c r="Q43" s="6"/>
     </row>
     <row r="44" spans="2:17">
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
       <c r="D44" s="22">
         <v>0.47207071</v>
       </c>
@@ -7458,17 +8692,17 @@
       <c r="K44" s="22">
         <v>0.11253626999999999</v>
       </c>
-      <c r="M44" s="32"/>
-      <c r="N44" s="32"/>
-      <c r="O44" s="32"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
       <c r="P44" s="20">
         <v>8.4729363200000005</v>
       </c>
       <c r="Q44" s="6"/>
     </row>
     <row r="45" spans="2:17">
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="38"/>
       <c r="D45" s="22">
         <v>0.85600695000000004</v>
       </c>
@@ -7493,17 +8727,17 @@
       <c r="K45" s="22">
         <v>0.96358986000000002</v>
       </c>
-      <c r="M45" s="32"/>
-      <c r="N45" s="32"/>
-      <c r="O45" s="32"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
       <c r="P45" s="20">
         <v>7.97768459</v>
       </c>
       <c r="Q45" s="6"/>
     </row>
     <row r="46" spans="2:17">
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
       <c r="D46" s="22">
         <v>0.81003174</v>
       </c>
@@ -7528,17 +8762,17 @@
       <c r="K46" s="22">
         <v>0.89054867000000004</v>
       </c>
-      <c r="M46" s="32"/>
-      <c r="N46" s="32"/>
-      <c r="O46" s="32"/>
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
       <c r="P46" s="20">
         <v>7.4608721899999999</v>
       </c>
       <c r="Q46" s="6"/>
     </row>
     <row r="47" spans="2:17">
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
       <c r="D47" s="22">
         <v>0.79625252000000002</v>
       </c>
@@ -7563,17 +8797,17 @@
       <c r="K47" s="22">
         <v>0.38173436999999999</v>
       </c>
-      <c r="M47" s="32"/>
-      <c r="N47" s="32"/>
-      <c r="O47" s="32"/>
+      <c r="M47" s="38"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="38"/>
       <c r="P47" s="20">
         <v>7.4365935299999997</v>
       </c>
       <c r="Q47" s="6"/>
     </row>
     <row r="48" spans="2:17">
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="38"/>
       <c r="D48" s="22">
         <v>0.48124533000000003</v>
       </c>
@@ -7598,9 +8832,9 @@
       <c r="K48" s="22">
         <v>0.71596163999999995</v>
       </c>
-      <c r="M48" s="32"/>
-      <c r="N48" s="32"/>
-      <c r="O48" s="32"/>
+      <c r="M48" s="38"/>
+      <c r="N48" s="38"/>
+      <c r="O48" s="38"/>
       <c r="P48" s="20">
         <v>9.1830052500000008</v>
       </c>
@@ -7779,10 +9013,224 @@
       <c r="T54" s="5"/>
     </row>
     <row r="55" spans="2:20">
-      <c r="T55" s="2"/>
-    </row>
-    <row r="56" spans="2:20">
+      <c r="B55" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="23">
+        <v>3</v>
+      </c>
+      <c r="D55" s="27">
+        <v>0.28807199999999999</v>
+      </c>
+      <c r="E55" s="27">
+        <v>0.28832200000000002</v>
+      </c>
+      <c r="F55" s="27">
+        <v>0.288572</v>
+      </c>
+      <c r="G55" s="27">
+        <v>0.28882200000000002</v>
+      </c>
+      <c r="H55" s="27">
+        <v>0.289072</v>
+      </c>
+      <c r="I55" s="27">
+        <v>0.28932200000000002</v>
+      </c>
+      <c r="J55" s="27">
+        <v>0.289572</v>
+      </c>
+      <c r="K55" s="27">
+        <v>0.28982200000000002</v>
+      </c>
+      <c r="M55" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="N55" s="24">
+        <v>3</v>
+      </c>
+      <c r="O55" s="25"/>
+      <c r="P55" s="25">
+        <v>9.6148418288995998</v>
+      </c>
+      <c r="Q55" s="25"/>
+      <c r="R55" s="25"/>
+      <c r="S55" s="25"/>
+      <c r="T55" s="25"/>
+    </row>
+    <row r="56" spans="2:20" ht="57.6">
+      <c r="M56" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="N56" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R56" s="21">
+        <f>MAX(R53,P55)</f>
+        <v>9.6764425194349997</v>
+      </c>
+      <c r="S56" s="31" t="s">
+        <v>65</v>
+      </c>
       <c r="T56" s="2"/>
+    </row>
+    <row r="57" spans="2:20" ht="57.6">
+      <c r="M57" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R57" s="21">
+        <f>MAX(R53,P55)</f>
+        <v>9.6764425194349997</v>
+      </c>
+      <c r="S57" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="T57" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:20">
+      <c r="B58" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="23">
+        <v>4</v>
+      </c>
+      <c r="D58" s="27">
+        <v>0.20405100000000001</v>
+      </c>
+      <c r="E58" s="27">
+        <v>0.20430100000000001</v>
+      </c>
+      <c r="F58" s="27">
+        <v>0.20455100000000001</v>
+      </c>
+      <c r="G58" s="27">
+        <v>0.20480100000000001</v>
+      </c>
+      <c r="H58" s="27">
+        <v>0.20505100000000001</v>
+      </c>
+      <c r="I58" s="27">
+        <v>0.20530100000000001</v>
+      </c>
+      <c r="J58" s="27">
+        <v>0.20555100000000001</v>
+      </c>
+      <c r="K58" s="27">
+        <v>0.20580100000000001</v>
+      </c>
+      <c r="M58" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="24">
+        <v>4</v>
+      </c>
+      <c r="O58" s="25"/>
+      <c r="P58" s="25">
+        <v>9.6762909065294007</v>
+      </c>
+      <c r="Q58" s="25"/>
+      <c r="R58" s="25"/>
+      <c r="S58" s="25"/>
+      <c r="T58" s="25"/>
+    </row>
+    <row r="59" spans="2:20" ht="57.6">
+      <c r="M59" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R59" s="21">
+        <f>MAX(R57,P58)</f>
+        <v>9.6764425194349997</v>
+      </c>
+      <c r="S59" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="T59" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:20">
+      <c r="B60" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="23">
+        <v>5</v>
+      </c>
+      <c r="D60" s="27">
+        <v>0.21205299999999999</v>
+      </c>
+      <c r="E60" s="27">
+        <v>0.21230299999999999</v>
+      </c>
+      <c r="F60" s="27">
+        <v>0.21255299999999999</v>
+      </c>
+      <c r="G60" s="27">
+        <v>0.21280299999999999</v>
+      </c>
+      <c r="H60" s="27">
+        <v>0.21305299999999999</v>
+      </c>
+      <c r="I60" s="27">
+        <v>0.21330299999999999</v>
+      </c>
+      <c r="J60" s="27">
+        <v>0.21355299999999999</v>
+      </c>
+      <c r="K60" s="27">
+        <v>0.21380299999999999</v>
+      </c>
+      <c r="M60" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="24">
+        <v>5</v>
+      </c>
+      <c r="O60" s="24"/>
+      <c r="P60" s="25">
+        <v>9.6768866362245998</v>
+      </c>
+      <c r="Q60" s="24"/>
+      <c r="R60" s="24"/>
+      <c r="S60" s="24"/>
+      <c r="T60" s="24"/>
+    </row>
+    <row r="61" spans="2:20" ht="57.6">
+      <c r="M61" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R61" s="21">
+        <f>MAX(R59,P60)</f>
+        <v>9.6768866362245998</v>
+      </c>
+      <c r="S61" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="T61" s="29" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/WeeklyPredictions.xlsx
+++ b/WeeklyPredictions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkArea\Workspaces\ProfessionalCourses\AI-ML_CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369F7F80-D2F0-4658-A85A-78463E02E457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B882584D-066F-4F49-A138-B210D507CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58440" yWindow="600" windowWidth="36765" windowHeight="19575" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61110" yWindow="825" windowWidth="32415" windowHeight="18675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Function 1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="103">
   <si>
     <t>Input (feature) dimension:</t>
   </si>
@@ -481,6 +481,42 @@
   </si>
   <si>
     <t>[0.070000, 0.046261, 0.100000, 0.100000, 0.047011, 0.047261, 0.047511, 0.047761]</t>
+  </si>
+  <si>
+    <t>[0.794794, 0.795795]</t>
+  </si>
+  <si>
+    <t>[0.512512, 0.513513]</t>
+  </si>
+  <si>
+    <t>[0.450000, 0.500000, 0.500000]</t>
+  </si>
+  <si>
+    <t>Confidence interval/ETA</t>
+  </si>
+  <si>
+    <t>eta = 0.01</t>
+  </si>
+  <si>
+    <t>Matern(length_scale=0.1, length_scale_bounds=(1e-3, 1e3), nu=1.5)</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>[0.360180, 0.360680, 0.361180, 0.361680]</t>
+  </si>
+  <si>
+    <t>[1.000000, 0.400000, 1.000000, 1.000000]</t>
+  </si>
+  <si>
+    <t>[0.420168, 0.420568, 0.420968, 0.700000, 0.060000]</t>
+  </si>
+  <si>
+    <t>[0.366122, 0.366455, 0.366788, 0.367122, 0.367455, 0.680000]</t>
+  </si>
+  <si>
+    <t>[0.015000, 0.190000, 0.000000, 0.000000, 0.190000, 0.190000, 0.190000, 0.190000]</t>
   </si>
 </sst>
 </file>
@@ -744,7 +780,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -875,6 +911,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1179,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:N31"/>
+  <dimension ref="B3:N35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.3125" customWidth="1"/>
@@ -1736,6 +1790,86 @@
         <v>1</v>
       </c>
     </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="23">
+        <v>6</v>
+      </c>
+      <c r="D32" s="27">
+        <v>0.384384</v>
+      </c>
+      <c r="E32" s="27">
+        <v>0.38538499999999998</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="24">
+        <v>6</v>
+      </c>
+      <c r="I32" s="24"/>
+      <c r="J32" s="28">
+        <v>1.54339407934348E-4</v>
+      </c>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
+    </row>
+    <row r="33" spans="2:14" ht="43.2">
+      <c r="G33" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L33" s="13">
+        <f>MAX(L31,J32)</f>
+        <v>1.54339407934348E-4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="23">
+        <v>7</v>
+      </c>
+      <c r="D34" s="27">
+        <v>0.794794</v>
+      </c>
+      <c r="E34" s="27">
+        <v>0.79579500000000003</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H34" s="24">
+        <v>7</v>
+      </c>
+      <c r="I34" s="24"/>
+      <c r="J34" s="28">
+        <v>3.8815429764520301E-39</v>
+      </c>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+      <c r="N34" s="24"/>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="L35" s="13">
+        <f>MAX(L33,J34)</f>
+        <v>1.54339407934348E-4</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B9:C18"/>
@@ -1752,7 +1886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{670CB941-049A-4FC0-8F09-1656ED8CE3C7}">
-  <dimension ref="B3:N32"/>
+  <dimension ref="B3:N36"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -2316,6 +2450,84 @@
         <v>1</v>
       </c>
     </row>
+    <row r="33" spans="2:13">
+      <c r="B33" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="23">
+        <v>6</v>
+      </c>
+      <c r="D33" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E33" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="24">
+        <v>6</v>
+      </c>
+      <c r="I33" s="24"/>
+      <c r="J33" s="26">
+        <v>0.52262959533611497</v>
+      </c>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+    </row>
+    <row r="34" spans="2:13" ht="43.2">
+      <c r="G34" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="21">
+        <f>MAX(L32,J33)</f>
+        <v>0.70032323557308995</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
+      <c r="B35" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="23">
+        <v>7</v>
+      </c>
+      <c r="D35" s="27">
+        <v>0.51251199999999997</v>
+      </c>
+      <c r="E35" s="27">
+        <v>0.513513</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="24">
+        <v>7</v>
+      </c>
+      <c r="I35" s="24"/>
+      <c r="J35" s="26">
+        <v>0.61916671697804904</v>
+      </c>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+    </row>
+    <row r="36" spans="2:13">
+      <c r="L36" s="21">
+        <f>MAX(L34,J35)</f>
+        <v>0.70032323557308995</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B4:C4"/>
@@ -2332,7 +2544,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31898AF6-32B3-4A29-BBAB-B50A72E3787B}">
-  <dimension ref="B3:O36"/>
+  <dimension ref="B3:O40"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -3033,6 +3245,86 @@
         <v>1</v>
       </c>
     </row>
+    <row r="37" spans="2:15">
+      <c r="B37" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="23">
+        <v>6</v>
+      </c>
+      <c r="D37" s="27">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="E37" s="27">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F37" s="27">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I37" s="24">
+        <v>6</v>
+      </c>
+      <c r="J37" s="24"/>
+      <c r="K37" s="26">
+        <v>-2.5600644844795201E-2</v>
+      </c>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+    </row>
+    <row r="38" spans="2:15" ht="28.8">
+      <c r="H38" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="21">
+        <f>MAX(M36,K37)</f>
+        <v>-3.7555388348285302E-3</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="B39" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="23">
+        <v>7</v>
+      </c>
+      <c r="D39" s="27">
+        <v>0.45</v>
+      </c>
+      <c r="E39" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="F39" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I39" s="24">
+        <v>7</v>
+      </c>
+      <c r="J39" s="24"/>
+      <c r="K39" s="26">
+        <v>-3.7555388348285302E-3</v>
+      </c>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+    </row>
+    <row r="40" spans="2:15">
+      <c r="M40" s="21">
+        <f>MAX(M38,K39)</f>
+        <v>-3.7555388348285302E-3</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B9:C23"/>
@@ -3050,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7581826F-7241-48DF-A0E8-08483F533A08}">
-  <dimension ref="B3:P50"/>
+  <dimension ref="B3:P54"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -3111,31 +3403,31 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="21.3">
+    <row r="8" spans="2:16" ht="28.8">
       <c r="B8" s="41"/>
       <c r="C8" s="41"/>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="15" t="s">
+      <c r="J8" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="47" t="s">
         <v>10</v>
       </c>
       <c r="M8" s="1"/>
@@ -4145,6 +4437,98 @@
       </c>
       <c r="P50" s="32" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16">
+      <c r="B51" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="23">
+        <v>6</v>
+      </c>
+      <c r="D51" s="27">
+        <v>0.35817900000000003</v>
+      </c>
+      <c r="E51" s="27">
+        <v>0.35867900000000003</v>
+      </c>
+      <c r="F51" s="27">
+        <v>0.35917900000000003</v>
+      </c>
+      <c r="G51" s="27">
+        <v>0.35967900000000003</v>
+      </c>
+      <c r="I51" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J51" s="24">
+        <v>6</v>
+      </c>
+      <c r="K51" s="24"/>
+      <c r="L51" s="26">
+        <v>0.73775846532035805</v>
+      </c>
+      <c r="M51" s="24"/>
+      <c r="N51" s="24"/>
+      <c r="O51" s="24"/>
+      <c r="P51" s="24"/>
+    </row>
+    <row r="52" spans="2:16" ht="43.2">
+      <c r="I52" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="N52" s="21">
+        <f>MAX(N50,L51)</f>
+        <v>0.73775846532035805</v>
+      </c>
+      <c r="O52" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16">
+      <c r="B53" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="23">
+        <v>7</v>
+      </c>
+      <c r="D53" s="27">
+        <v>0.36018</v>
+      </c>
+      <c r="E53" s="27">
+        <v>0.36068</v>
+      </c>
+      <c r="F53" s="27">
+        <v>0.36118</v>
+      </c>
+      <c r="G53" s="27">
+        <v>0.36168</v>
+      </c>
+      <c r="I53" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J53" s="24">
+        <v>7</v>
+      </c>
+      <c r="K53" s="24"/>
+      <c r="L53" s="26">
+        <v>0.74717522483983601</v>
+      </c>
+      <c r="M53" s="24"/>
+      <c r="N53" s="24"/>
+      <c r="O53" s="24"/>
+      <c r="P53" s="24"/>
+    </row>
+    <row r="54" spans="2:16">
+      <c r="N54" s="21">
+        <f>MAX(N52,L53)</f>
+        <v>0.74717522483983601</v>
       </c>
     </row>
   </sheetData>
@@ -4164,7 +4548,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB787A30-BB0A-4678-A75A-EF41DE76C694}">
-  <dimension ref="B3:P40"/>
+  <dimension ref="B3:P44"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -5020,6 +5404,92 @@
         <v>1</v>
       </c>
     </row>
+    <row r="41" spans="2:16">
+      <c r="B41" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="23">
+        <v>6</v>
+      </c>
+      <c r="D41" s="27">
+        <v>0.99849900000000003</v>
+      </c>
+      <c r="E41" s="27">
+        <v>0.99899899999999997</v>
+      </c>
+      <c r="F41" s="27">
+        <v>0.99949900000000003</v>
+      </c>
+      <c r="G41" s="27">
+        <v>1</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="24">
+        <v>6</v>
+      </c>
+      <c r="K41" s="24"/>
+      <c r="L41" s="26">
+        <v>8604.4979780305202</v>
+      </c>
+      <c r="M41" s="24"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="24"/>
+    </row>
+    <row r="42" spans="2:16" ht="28.8">
+      <c r="I42" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" s="21">
+        <f>MAX(N40,L41)</f>
+        <v>8662.4825000000001</v>
+      </c>
+      <c r="O42" s="19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16">
+      <c r="B43" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="23">
+        <v>7</v>
+      </c>
+      <c r="D43" s="27">
+        <v>1</v>
+      </c>
+      <c r="E43" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="F43" s="27">
+        <v>1</v>
+      </c>
+      <c r="G43" s="27">
+        <v>1</v>
+      </c>
+      <c r="I43" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="24">
+        <v>7</v>
+      </c>
+      <c r="K43" s="24"/>
+      <c r="L43" s="26">
+        <v>4540.3798008896001</v>
+      </c>
+      <c r="M43" s="24"/>
+      <c r="N43" s="24"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="24"/>
+    </row>
+    <row r="44" spans="2:16">
+      <c r="N44" s="21">
+        <f>MAX(N42,L43)</f>
+        <v>8662.4825000000001</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B9:C28"/>
@@ -5037,7 +5507,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B451910E-E097-46FF-B069-9F3B8C7F2915}">
-  <dimension ref="B3:Q41"/>
+  <dimension ref="B3:Q45"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -5996,6 +6466,99 @@
         <v>1</v>
       </c>
     </row>
+    <row r="42" spans="2:17">
+      <c r="B42" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="23">
+        <v>6</v>
+      </c>
+      <c r="D42" s="27">
+        <v>0.45218000000000003</v>
+      </c>
+      <c r="E42" s="27">
+        <v>0.45258100000000001</v>
+      </c>
+      <c r="F42" s="27">
+        <v>0.45298100000000002</v>
+      </c>
+      <c r="G42" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="H42" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="J42" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="K42" s="24">
+        <v>6</v>
+      </c>
+      <c r="L42" s="24"/>
+      <c r="M42" s="26">
+        <v>-0.49607977761293698</v>
+      </c>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
+    </row>
+    <row r="43" spans="2:17" ht="43.2">
+      <c r="J43" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="O43" s="21">
+        <f>MAX(O41,M42)</f>
+        <v>-0.49607977761293698</v>
+      </c>
+      <c r="P43" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17">
+      <c r="B44" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="23">
+        <v>7</v>
+      </c>
+      <c r="D44" s="27">
+        <v>0.45218000000000003</v>
+      </c>
+      <c r="E44" s="27">
+        <v>0.45258100000000001</v>
+      </c>
+      <c r="F44" s="27">
+        <v>0.45298100000000002</v>
+      </c>
+      <c r="G44" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="H44" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="J44" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="24">
+        <v>7</v>
+      </c>
+      <c r="L44" s="24"/>
+      <c r="M44" s="26">
+        <v>-0.39276604451561498</v>
+      </c>
+      <c r="N44" s="24"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="24"/>
+      <c r="Q44" s="24"/>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="M45" s="20"/>
+      <c r="O45" s="21">
+        <f>MAX(O43,M44)</f>
+        <v>-0.39276604451561498</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B9:C28"/>
@@ -6013,7 +6576,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B58C19-2A2F-49AE-AB19-E8DF9CAE3947}">
-  <dimension ref="B3:R50"/>
+  <dimension ref="B3:R54"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -7245,6 +7808,12 @@
       <c r="K48" s="19" t="s">
         <v>76</v>
       </c>
+      <c r="L48" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="P48" s="21">
         <f>MAX(P46,N47)</f>
         <v>1.8037650755561301</v>
@@ -7300,6 +7869,12 @@
       <c r="K50" s="19" t="s">
         <v>84</v>
       </c>
+      <c r="L50" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="P50" s="21">
         <f>MAX(P48,N49)</f>
         <v>1.8037650755561301</v>
@@ -7309,6 +7884,110 @@
       </c>
       <c r="R50" s="29" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18">
+      <c r="B51" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="23">
+        <v>6</v>
+      </c>
+      <c r="D51" s="27">
+        <v>0.33411099999999999</v>
+      </c>
+      <c r="E51" s="27">
+        <v>0.33444400000000002</v>
+      </c>
+      <c r="F51" s="27">
+        <v>0.33477800000000002</v>
+      </c>
+      <c r="G51" s="27">
+        <v>0.33511099999999999</v>
+      </c>
+      <c r="H51" s="27">
+        <v>0.33544499999999999</v>
+      </c>
+      <c r="I51" s="27">
+        <v>0.68</v>
+      </c>
+      <c r="K51" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="L51" s="24">
+        <v>6</v>
+      </c>
+      <c r="M51" s="24"/>
+      <c r="N51" s="26">
+        <v>2.5841859527428799</v>
+      </c>
+      <c r="O51" s="24"/>
+      <c r="P51" s="24"/>
+      <c r="Q51" s="24"/>
+      <c r="R51" s="24"/>
+    </row>
+    <row r="52" spans="2:18" ht="43.2">
+      <c r="K52" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P52" s="21">
+        <f>MAX(P50,N51)</f>
+        <v>2.5841859527428799</v>
+      </c>
+      <c r="Q52" s="19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18">
+      <c r="B53" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="23">
+        <v>7</v>
+      </c>
+      <c r="D53" s="27">
+        <v>0.366122</v>
+      </c>
+      <c r="E53" s="27">
+        <v>0.36645499999999998</v>
+      </c>
+      <c r="F53" s="27">
+        <v>0.366788</v>
+      </c>
+      <c r="G53" s="27">
+        <v>0.367122</v>
+      </c>
+      <c r="H53" s="27">
+        <v>0.36745499999999998</v>
+      </c>
+      <c r="I53" s="27">
+        <v>0.68</v>
+      </c>
+      <c r="K53" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="L53" s="24">
+        <v>7</v>
+      </c>
+      <c r="M53" s="24"/>
+      <c r="N53" s="26">
+        <v>2.2258662517679002</v>
+      </c>
+      <c r="O53" s="24"/>
+      <c r="P53" s="24"/>
+      <c r="Q53" s="24"/>
+      <c r="R53" s="24"/>
+    </row>
+    <row r="54" spans="2:18">
+      <c r="P54" s="21">
+        <f>MAX(P52,N53)</f>
+        <v>2.5841859527428799</v>
       </c>
     </row>
   </sheetData>
@@ -7328,7 +8007,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0AA28BB-74D8-433B-A00A-14B553BBFF2F}">
-  <dimension ref="B3:T61"/>
+  <dimension ref="B3:T65"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.734375" customWidth="1"/>
@@ -9232,6 +9911,116 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="2:20">
+      <c r="B62" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" s="23">
+        <v>6</v>
+      </c>
+      <c r="D62" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E62" s="27">
+        <v>4.6260999999999997E-2</v>
+      </c>
+      <c r="F62" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="G62" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="H62" s="27">
+        <v>4.7010999999999997E-2</v>
+      </c>
+      <c r="I62" s="27">
+        <v>4.7260999999999997E-2</v>
+      </c>
+      <c r="J62" s="27">
+        <v>4.7510999999999998E-2</v>
+      </c>
+      <c r="K62" s="27">
+        <v>4.7760999999999998E-2</v>
+      </c>
+      <c r="M62" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="24">
+        <v>6</v>
+      </c>
+      <c r="O62" s="24"/>
+      <c r="P62" s="25">
+        <v>9.4167668191433993</v>
+      </c>
+      <c r="Q62" s="24"/>
+      <c r="R62" s="24"/>
+      <c r="S62" s="24"/>
+      <c r="T62" s="24"/>
+    </row>
+    <row r="63" spans="2:20" ht="57.6">
+      <c r="M63" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="R63" s="21">
+        <f>MAX(R61,P62)</f>
+        <v>9.6768866362245998</v>
+      </c>
+      <c r="S63" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="2:20">
+      <c r="B64" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" s="23">
+        <v>7</v>
+      </c>
+      <c r="D64" s="27">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E64" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="F64" s="27">
+        <v>0</v>
+      </c>
+      <c r="G64" s="27">
+        <v>0</v>
+      </c>
+      <c r="H64" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="I64" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="J64" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="K64" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="M64" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="N64" s="24">
+        <v>7</v>
+      </c>
+      <c r="O64" s="24"/>
+      <c r="P64" s="25">
+        <v>9.6115899999999996</v>
+      </c>
+      <c r="Q64" s="24"/>
+      <c r="R64" s="24"/>
+      <c r="S64" s="24"/>
+      <c r="T64" s="24"/>
+    </row>
+    <row r="65" spans="18:18">
+      <c r="R65" s="21">
+        <f>MAX(R63,P64)</f>
+        <v>9.6768866362245998</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B9:C48"/>
